--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CF2479-B430-614A-9D33-50B4B68DD3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C30776-8C72-4F77-9DE0-8EFBBECBD651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2499,7 +2488,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3874,30 +3863,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3912,7 +3901,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4201,7 +4190,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4210,7 +4199,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4227,7 +4216,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4241,7 +4230,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>420</v>
       </c>
@@ -4250,7 +4239,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>317</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4267,7 +4256,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>309</v>
       </c>
@@ -4277,7 +4266,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4287,17 +4276,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>423</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>422</v>
       </c>
@@ -4307,7 +4296,7 @@
       <c r="D11" s="49"/>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4317,7 +4306,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>421</v>
       </c>
@@ -4327,7 +4316,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>425</v>
       </c>
@@ -4341,7 +4330,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>424</v>
       </c>
@@ -4355,7 +4344,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4365,27 +4354,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="349" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>308</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>351</v>
       </c>
@@ -4400,7 +4389,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4413,7 +4402,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>439</v>
       </c>
@@ -4421,7 +4410,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>440</v>
       </c>
@@ -4429,7 +4418,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>350</v>
       </c>
@@ -4445,7 +4434,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4462,11 +4451,11 @@
         <v>6.5930019453462219E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>438</v>
       </c>
@@ -4485,13 +4474,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>430</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>9.9844905090753358</v>
+        <v>11.355103666814504</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4501,16 +4490,16 @@
         <v>429</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>431</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>14.693235313144449</v>
+        <v>15.879140273250821</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4520,10 +4509,10 @@
         <v>442</v>
       </c>
       <c r="F30" s="342">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.187</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>432</v>
       </c>
@@ -4542,13 +4531,13 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>433</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>18.729274352068373</v>
+        <v>20.396738931178472</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4558,14 +4547,14 @@
         <v>443</v>
       </c>
       <c r="F32" s="342">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>358</v>
       </c>
@@ -4575,25 +4564,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="349" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="352" t="s">
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="349" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4602,16 +4591,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="350" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4624,20 +4613,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="350" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4650,7 +4639,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4663,16 +4652,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="350" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4685,16 +4674,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="350" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
@@ -4709,7 +4698,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
@@ -4724,7 +4713,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4737,12 +4726,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4755,16 +4744,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="350" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4777,8 +4766,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="350" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="348" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="351"/>
@@ -4786,7 +4775,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4799,25 +4788,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="349" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="347" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="349" t="s">
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4830,7 +4819,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4843,7 +4832,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>394</v>
       </c>
@@ -4853,7 +4842,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>310</v>
       </c>
@@ -4869,7 +4858,7 @@
         <v>1.0164059245889612</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>359</v>
       </c>
@@ -4879,34 +4868,34 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="352" t="s">
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
+    </row>
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>436</v>
       </c>
@@ -4915,7 +4904,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>435</v>
       </c>
@@ -4924,7 +4913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
@@ -4933,34 +4922,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>360</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="349" t="s">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B83" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
-    </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="349" t="s">
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B84" s="347" t="s">
         <v>368</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
+    </row>
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4968,7 +4957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
@@ -4981,7 +4970,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>361</v>
       </c>
@@ -4991,38 +4980,38 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="349" t="s">
+    <row r="91" spans="1:6">
+      <c r="B91" s="347" t="s">
         <v>369</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="349" t="s">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B95" s="347" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
+    </row>
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5035,7 +5024,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5048,7 +5037,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>408</v>
       </c>
@@ -5057,7 +5046,7 @@
         <v>0.27606884288300854</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>409</v>
       </c>
@@ -5066,7 +5055,7 @@
         <v>0.12757636177577109</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>411</v>
       </c>
@@ -5075,12 +5064,12 @@
         <v>0.79731882844192148</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5093,7 +5082,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5106,7 +5095,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5119,12 +5108,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5137,7 +5126,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5150,16 +5139,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="349" t="s">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B111" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
+    </row>
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>454</v>
       </c>
@@ -5172,7 +5161,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>410</v>
       </c>
@@ -5185,7 +5174,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>362</v>
       </c>
@@ -5195,16 +5184,16 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="350" t="s">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B118" s="348" t="s">
         <v>371</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
-    </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5221,7 +5210,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5243,7 +5232,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5265,7 +5254,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5287,7 +5276,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5309,7 +5298,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5331,7 +5320,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
@@ -5344,16 +5333,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="353" t="s">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B129" s="352" t="s">
         <v>374</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
-    </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>406</v>
       </c>
@@ -5363,30 +5352,30 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="354" t="s">
+    <row r="133" spans="1:6">
+      <c r="B133" s="350" t="s">
         <v>372</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
-    </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="349" t="s">
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="347" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
+    </row>
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5395,16 +5384,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5417,7 +5406,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>413</v>
       </c>
@@ -5430,49 +5419,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>412</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>1.7478134110787167</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>1.8983532786438633</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>8.2366770979966191</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>9.4567503881706401</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>9.9844905090753358</v>
+        <v>11.355103666814504</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>421</v>
       </c>
@@ -5485,63 +5474,63 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55823657056420828</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.4975938398768166</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>415</v>
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.187</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>2.2464655631969199</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+        <v>2.365137899745049</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>12.446769749947528</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>13.514002373505772</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>14.693235313144449</v>
+        <v>15.879140273250821</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>421</v>
       </c>
@@ -5554,21 +5543,21 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34989832325025705</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.29742800023424332</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>414</v>
       </c>
@@ -5577,7 +5566,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5587,7 +5576,7 @@
         <v>2.9403131444078037</v>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5597,7 +5586,7 @@
         <v>18.976606491350839</v>
       </c>
     </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>405</v>
       </c>
@@ -5610,7 +5599,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>421</v>
       </c>
@@ -5623,7 +5612,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
@@ -5632,54 +5621,54 @@
         <v>3.0286665888368924E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C166" s="238">
         <f>Scenarios!C103</f>
-        <v>2.6420143950437343</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2.7993790642942851</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>16.087259957024639</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>17.597359866884187</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>405</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>18.729274352068373</v>
+        <v>20.396738931178472</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>421</v>
       </c>
@@ -5692,16 +5681,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.19165828757230807</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.11969174215505207</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>378</v>
       </c>
@@ -5711,21 +5700,21 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="348" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="354" t="s">
         <v>380</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
+    </row>
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>384</v>
       </c>
@@ -5734,80 +5723,91 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="350" t="s">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="348" t="s">
         <v>385</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
-    </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
+    </row>
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="347" t="s">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B186" s="353" t="s">
         <v>386</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
-    </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="347" t="s">
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B187" s="353" t="s">
         <v>387</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
-    </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
+    </row>
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5824,17 +5824,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5865,15 +5854,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5922,7 +5911,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5938,7 +5927,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5946,7 +5935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5982,7 +5971,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6018,7 +6007,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6054,7 +6043,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6090,7 +6079,7 @@
       </c>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6106,7 +6095,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6122,7 +6111,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6138,7 +6127,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6154,7 +6143,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6184,7 +6173,7 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6214,7 +6203,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6250,7 +6239,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6286,7 +6275,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6322,13 +6311,13 @@
       </c>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6358,7 +6347,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6374,7 +6363,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6390,7 +6379,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>375</v>
       </c>
@@ -6426,7 +6415,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>377</v>
       </c>
@@ -6462,7 +6451,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>376</v>
       </c>
@@ -6498,7 +6487,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6524,7 +6513,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6532,7 +6521,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6569,7 +6558,7 @@
       </c>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6606,7 +6595,7 @@
       </c>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6643,7 +6632,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6680,7 +6669,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6717,7 +6706,7 @@
       </c>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6733,12 +6722,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6787,7 +6776,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6836,7 +6825,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6885,7 +6874,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6934,7 +6923,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6983,7 +6972,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7032,7 +7021,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7081,7 +7070,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7130,7 +7119,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7179,7 +7168,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7228,7 +7217,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7277,7 +7266,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7326,7 +7315,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7375,12 +7364,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7429,7 +7418,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7478,12 +7467,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7532,7 +7521,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7581,7 +7570,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7630,7 +7619,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7679,13 +7668,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7734,7 +7723,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7783,7 +7772,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7832,7 +7821,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>397</v>
       </c>
@@ -7881,7 +7870,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7930,12 +7919,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7985,7 +7974,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8034,7 +8023,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8084,7 +8073,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8133,7 +8122,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8183,7 +8172,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8199,13 +8188,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8254,7 +8243,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8288,7 +8277,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8322,7 +8311,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8371,7 +8360,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8452,7 +8441,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8463,7 +8452,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8479,7 +8468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8490,7 +8479,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8510,7 +8499,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8532,7 +8521,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8553,7 +8542,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8574,7 +8563,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8595,7 +8584,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8616,7 +8605,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8637,7 +8626,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8649,7 +8638,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8661,7 +8650,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8685,12 +8674,12 @@
         <v>3587495939.0999999</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8710,7 +8699,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8730,7 +8719,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8750,7 +8739,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8770,7 +8759,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8790,7 +8779,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8811,7 +8800,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8831,7 +8820,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8851,7 +8840,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8863,7 +8852,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8876,7 +8865,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8900,7 +8889,7 @@
         <v>601196473.00000012</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8917,7 +8906,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8936,7 +8925,7 @@
         <v>2595022082.4499998</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8951,7 +8940,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8970,7 +8959,7 @@
         <v>2590063727.4499998</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8986,7 +8975,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -9003,7 +8992,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9023,7 +9012,7 @@
         <v>5261305585.4499998</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9034,7 +9023,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -9047,7 +9036,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9066,7 +9055,7 @@
         <v>1072613173.35</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9082,7 +9071,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9098,7 +9087,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9114,7 +9103,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9133,7 +9122,7 @@
         <v>3504047.1</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9153,7 +9142,7 @@
         <v>4188692412.0999999</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9173,7 +9162,7 @@
         <v>3587495939.8999996</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9192,7 +9181,7 @@
         <v>601196472.20000005</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9203,7 +9192,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9217,7 +9206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9231,7 +9220,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9246,10 +9235,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9262,7 +9251,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9276,7 +9265,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9287,10 +9276,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9302,7 +9291,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9316,7 +9305,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9330,10 +9319,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9345,7 +9334,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9356,7 +9345,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9367,10 +9356,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9382,7 +9371,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9398,7 +9387,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9409,7 +9398,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9423,7 +9412,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9439,7 +9428,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9449,7 +9438,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9459,7 +9448,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9469,7 +9458,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9479,10 +9468,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>320</v>
       </c>
@@ -9494,7 +9483,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>319</v>
       </c>
@@ -9510,7 +9499,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>324</v>
       </c>
@@ -9526,7 +9515,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>322</v>
       </c>
@@ -9539,7 +9528,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>325</v>
       </c>
@@ -9552,10 +9541,10 @@
         <v>326</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9567,7 +9556,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9581,7 +9570,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9595,7 +9584,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9609,7 +9598,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9623,7 +9612,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>290</v>
       </c>
@@ -9634,7 +9623,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>291</v>
       </c>
@@ -9642,7 +9631,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>288</v>
       </c>
@@ -9659,7 +9648,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>289</v>
       </c>
@@ -9676,7 +9665,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9693,7 +9682,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>293</v>
       </c>
@@ -9724,19 +9713,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9793,7 +9782,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9816,7 +9805,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9830,7 +9819,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9887,7 +9876,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9942,7 +9931,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9997,7 +9986,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10052,7 +10041,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10109,7 +10098,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10164,7 +10153,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10219,7 +10208,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10276,7 +10265,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10331,7 +10320,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10386,7 +10375,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10441,7 +10430,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10498,7 +10487,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10555,7 +10544,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10581,7 +10570,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10606,7 +10595,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10663,7 +10652,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10682,7 +10671,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10705,7 +10694,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10726,7 +10715,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10783,7 +10772,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10840,7 +10829,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10897,18 +10886,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10967,7 +10956,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11027,7 +11016,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11082,18 +11071,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11150,7 +11139,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11209,7 +11198,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11266,18 +11255,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11335,7 +11324,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11393,7 +11382,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11448,18 +11437,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11517,10 +11506,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11543,14 +11532,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11605,7 +11594,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>348</v>
@@ -11660,7 +11649,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>345</v>
@@ -11717,7 +11706,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11772,11 +11761,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11786,7 +11775,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11812,7 +11801,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11839,7 +11828,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11894,11 +11883,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11908,7 +11897,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11963,7 +11952,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -12018,7 +12007,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12073,7 +12062,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12128,7 +12117,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12184,7 +12173,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12239,11 +12228,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12253,7 +12242,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12278,7 +12267,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12303,7 +12292,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12328,7 +12317,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12355,10 +12344,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12381,7 +12370,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12402,7 +12391,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12459,7 +12448,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12516,7 +12505,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12573,7 +12562,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12630,7 +12619,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12687,7 +12676,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12746,7 +12735,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12803,7 +12792,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12860,7 +12849,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12917,7 +12906,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12974,7 +12963,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13032,7 +13021,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13089,7 +13078,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13115,7 +13104,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13139,7 +13128,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13196,18 +13185,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13263,7 +13252,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13319,7 +13308,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13374,7 +13363,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>311</v>
@@ -13429,11 +13418,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13454,7 +13443,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13511,7 +13500,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13568,10 +13557,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13594,7 +13583,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13604,7 +13593,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13661,7 +13650,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13718,7 +13707,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13775,7 +13764,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13832,7 +13821,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13889,11 +13878,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13916,7 +13905,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13973,7 +13962,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -14030,7 +14019,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14057,18 +14046,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>395</v>
@@ -14120,7 +14109,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>396</v>
@@ -14172,11 +14161,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14230,7 +14219,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14285,7 +14274,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14339,7 +14328,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14395,7 +14384,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14452,7 +14441,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14471,7 +14460,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14494,7 +14483,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14515,7 +14504,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14573,7 +14562,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14630,7 +14619,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>398</v>
       </c>
@@ -14680,688 +14669,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15383,16 +15372,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15404,7 +15393,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15417,7 +15406,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15438,7 +15427,7 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
@@ -15449,7 +15438,7 @@
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
@@ -15467,7 +15456,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15483,7 +15472,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15499,7 +15488,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15515,7 +15504,7 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
@@ -15529,7 +15518,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15543,7 +15532,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
@@ -15557,10 +15546,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15570,13 +15559,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15586,7 +15575,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15596,7 +15585,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
@@ -15610,10 +15599,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15631,7 +15620,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15653,7 +15642,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15675,7 +15664,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15697,7 +15686,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15719,7 +15708,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15741,7 +15730,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15763,7 +15752,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15785,7 +15774,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15807,7 +15796,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15829,7 +15818,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15851,7 +15840,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15873,7 +15862,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15895,7 +15884,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15917,7 +15906,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15939,7 +15928,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15961,7 +15950,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15983,7 +15972,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -16005,7 +15994,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -16027,7 +16016,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -16049,7 +16038,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -16071,7 +16060,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16093,7 +16082,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16115,7 +16104,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16137,7 +16126,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16159,7 +16148,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16181,7 +16170,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16203,7 +16192,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16225,7 +16214,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16247,7 +16236,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16269,7 +16258,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16291,7 +16280,7 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
@@ -16313,7 +16302,7 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
@@ -16324,11 +16313,11 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16338,7 +16327,7 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
         <v>20531263785.115158</v>
@@ -16365,7 +16354,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
@@ -16387,7 +16376,7 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
@@ -16408,7 +16397,7 @@
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
@@ -16429,7 +16418,7 @@
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
@@ -16450,7 +16439,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
@@ -16471,7 +16460,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
@@ -16492,14 +16481,14 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16509,7 +16498,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16532,7 +16521,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
@@ -16558,7 +16547,7 @@
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16585,7 +16574,7 @@
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16612,7 +16601,7 @@
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16639,7 +16628,7 @@
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16666,7 +16655,7 @@
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16692,7 +16681,7 @@
         <v>34.298144365868922</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16718,7 +16707,7 @@
         <v>38.583440282129665</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16735,7 +16724,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16757,7 +16746,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16780,7 +16769,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16803,7 +16792,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16826,7 +16815,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16848,14 +16837,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>312</v>
       </c>
@@ -16863,23 +16852,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16913,16 +16902,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>448</v>
       </c>
@@ -16934,7 +16923,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>447</v>
       </c>
@@ -16947,7 +16936,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>445</v>
       </c>
@@ -16968,7 +16957,7 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
@@ -16979,7 +16968,7 @@
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>446</v>
       </c>
@@ -16995,7 +16984,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>449</v>
       </c>
@@ -17009,10 +16998,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -17022,13 +17011,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -17038,7 +17027,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -17048,7 +17037,7 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
@@ -17062,10 +17051,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17083,7 +17072,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17105,7 +17094,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17127,7 +17116,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17149,7 +17138,7 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17171,7 +17160,7 @@
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17193,7 +17182,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17215,7 +17204,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17237,7 +17226,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17259,7 +17248,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17281,7 +17270,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17303,7 +17292,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17325,7 +17314,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17347,7 +17336,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17369,7 +17358,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17391,7 +17380,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17413,7 +17402,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17435,7 +17424,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17457,7 +17446,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17479,7 +17468,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17501,7 +17490,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17523,7 +17512,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17545,7 +17534,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17567,7 +17556,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17589,7 +17578,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17611,7 +17600,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17633,7 +17622,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17655,7 +17644,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17677,7 +17666,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17699,7 +17688,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17721,7 +17710,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17743,7 +17732,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
@@ -17765,7 +17754,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
@@ -17776,11 +17765,11 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17790,7 +17779,7 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
         <v>20868098150.489822</v>
@@ -17817,7 +17806,7 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
@@ -17839,7 +17828,7 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
@@ -17860,7 +17849,7 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
@@ -17881,7 +17870,7 @@
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
@@ -17902,7 +17891,7 @@
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
@@ -17923,7 +17912,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
@@ -17944,14 +17933,14 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17961,7 +17950,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -17984,7 +17973,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
@@ -18010,7 +17999,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18037,7 +18026,7 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18064,7 +18053,7 @@
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18091,7 +18080,7 @@
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18118,7 +18107,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18144,7 +18133,7 @@
         <v>32.027940052792374</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18170,7 +18159,7 @@
         <v>36.383540210696673</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18187,7 +18176,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18209,7 +18198,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18232,7 +18221,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18255,7 +18244,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18278,7 +18267,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18300,14 +18289,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>312</v>
       </c>
@@ -18315,23 +18304,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18361,7 +18350,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18371,7 +18360,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18384,7 +18373,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18396,7 +18385,7 @@
         <v>-21.57</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18416,7 +18405,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18425,7 +18414,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18445,7 +18434,7 @@
         <v>23.70144195690272</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18470,7 +18459,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18492,7 +18481,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18514,7 +18503,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18525,7 +18514,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>452</v>
       </c>
@@ -18539,7 +18528,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18558,7 +18547,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18576,7 +18565,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18587,7 +18576,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18596,7 +18585,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18604,7 +18593,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18616,18 +18605,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>305</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18642,7 +18631,7 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
@@ -18657,7 +18646,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18666,7 +18655,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18678,7 +18667,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18689,7 +18678,7 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
@@ -18704,7 +18693,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18715,7 +18704,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18724,7 +18713,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18736,7 +18725,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18747,7 +18736,7 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
@@ -18762,7 +18751,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18773,7 +18762,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18782,7 +18771,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18794,7 +18783,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18805,7 +18794,7 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
@@ -18820,7 +18809,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18832,7 +18821,7 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
@@ -18845,7 +18834,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18854,12 +18843,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18869,12 +18858,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18883,7 +18872,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18895,7 +18884,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18906,7 +18895,7 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
@@ -18921,7 +18910,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18932,7 +18921,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>318</v>
       </c>
@@ -18941,7 +18930,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18953,7 +18942,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18964,7 +18953,7 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
@@ -18979,7 +18968,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -18990,7 +18979,7 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
@@ -19010,7 +18999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>352</v>
       </c>
@@ -19019,7 +19008,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>306</v>
       </c>
@@ -19027,7 +19016,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -19040,7 +19029,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -19052,7 +19041,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
@@ -19068,7 +19057,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>353</v>
       </c>
@@ -19076,7 +19065,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>307</v>
       </c>
@@ -19086,7 +19075,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>295</v>
       </c>
@@ -19098,7 +19087,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>294</v>
       </c>
@@ -19108,7 +19097,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>286</v>
       </c>
@@ -19124,7 +19113,7 @@
         <v>0.12331828082950577</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19133,12 +19122,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>299</v>
       </c>
@@ -19148,7 +19137,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19161,49 +19150,49 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>301</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.7478134110787167</v>
+        <v>1.8983532786438633</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.2366770979966191</v>
+        <v>9.4567503881706401</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.9844905090753358</v>
+        <v>11.355103666814504</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19214,18 +19203,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.55823657056420828</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.4975938398768166</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>302</v>
       </c>
@@ -19238,7 +19227,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>300</v>
       </c>
@@ -19247,52 +19236,52 @@
         <v>6.5930019453462219E-2</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>418</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.187</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.2464655631969199</v>
+        <v>2.365137899745049</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>12.446769749947528</v>
+        <v>13.514002373505772</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>14.693235313144449</v>
+        <v>15.879140273250821</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19303,17 +19292,17 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.34989832325025705</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.29742800023424332</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>401</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>407</v>
       </c>
@@ -19324,7 +19313,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
@@ -19336,7 +19325,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
@@ -19348,7 +19337,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>402</v>
       </c>
@@ -19367,50 +19356,50 @@
         <v>3.0286665888368924E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>426</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.6420143950437343</v>
+        <v>2.7993790642942851</v>
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>16.087259957024639</v>
+        <v>17.597359866884187</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>402</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>18.729274352068373</v>
+        <v>20.396738931178472</v>
       </c>
       <c r="D105" t="s">
         <v>400</v>
@@ -19420,19 +19409,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.19165828757230807</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.11969174215505207</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>327</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>328</v>
       </c>
@@ -19440,7 +19429,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>328</v>
       </c>
@@ -19448,7 +19437,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>328</v>
       </c>

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAF3306-6E01-4F83-A706-80264C8C8591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16792DF-F84E-49BB-A721-EDF77B03A98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3868,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4308,7 +4308,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>21.57</v>
+        <v>21.69</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21727.08425838</v>
+        <v>21847.958162460003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4366,13 +4366,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>6.5930019453462219E-2</v>
+        <v>6.3864060260578226E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4497,7 +4497,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="305">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4572,22 +4572,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4599,13 +4599,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4625,13 +4625,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4660,13 +4660,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4752,13 +4752,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4796,22 +4796,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.0173610285274194E-2</v>
+        <v>4.9896024612879862E-2</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.0996754751970332E-2</v>
+        <v>5.0714615029967727E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4880,22 +4880,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4939,22 +4939,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4991,13 +4991,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5010,13 +5010,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5147,13 +5147,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5192,13 +5192,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5341,13 +5341,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5360,22 +5360,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C137" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C141" s="299">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="C142" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8983532786438631</v>
+        <v>1.8983532786438633</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5708,13 +5708,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5751,13 +5751,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5765,22 +5765,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5804,6 +5804,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5820,17 +5831,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13377,20 +13377,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.0996754751970332E-2</v>
+        <v>5.0714615029967727E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.0996754751970332E-2</v>
+        <v>5.0714615029967727E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.0268891979601301E-2</v>
+        <v>5.9935454126325491E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.2452480296708386E-2</v>
+        <v>3.2272936837252186E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14576,50 +14576,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0173610285274194E-2</v>
+        <v>4.9896024612879862E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.5128550235083791E-2</v>
+        <v>5.4823551340283876E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.5679949716833356E-2</v>
+        <v>5.537190020249403E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.2083894696884463E-2</v>
+        <v>4.185106540395564E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.4627971267061181E-2</v>
+        <v>4.4381066861710908E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4966805852330515E-2</v>
+        <v>3.4773351878043764E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.3156882067060857E-2</v>
+        <v>4.2918116467796343E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.5343473512964435E-2</v>
+        <v>3.5147935623542778E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.431162788041698E-2</v>
+        <v>3.4121798680525318E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.5122927583146363E-2</v>
+        <v>3.4928609864844029E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2587503485513328E-2</v>
+        <v>3.2407213009798173E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14633,43 +14633,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8154225986980626E-2</v>
+        <v>5.7832487530621118E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7996893739388246E-2</v>
+        <v>5.7676025724232569E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1403712974935276E-2</v>
+        <v>5.1119321755156925E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7157969602148346E-2</v>
+        <v>4.6897067972260939E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8023088426205484E-2</v>
+        <v>3.7812725558010706E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4786616300099641E-2</v>
+        <v>4.4538834190555515E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5691615993107967E-2</v>
+        <v>3.5494152004211098E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.925389943912296E-2</v>
+        <v>2.9092052139321447E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1615603310189276E-2</v>
+        <v>3.1440689875554755E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8916126735122446E-2</v>
+        <v>2.8756148163973771E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18389,7 +18389,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.57</v>
+        <v>-21.69</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.57</v>
+        <v>21.69</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8983532786438631</v>
+        <v>1.8983532786438633</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.57</v>
+        <v>21.69</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.5930019453462219E-2</v>
+        <v>6.3864060260578226E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0132936-1F5A-4330-8BB6-23EB947FF45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6ECEE7-08EF-4C00-962E-14A6F398532F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4322,7 +4322,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21847.958162460003</v>
+        <v>21827.812511780001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4380,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.3864060260578226E-2</v>
+        <v>6.4207293080563721E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4511,7 +4511,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4586,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,13 +4613,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4639,13 +4639,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4674,13 +4674,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4696,13 +4696,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4766,13 +4766,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4788,7 +4788,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4810,22 +4810,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.9896024612879862E-2</v>
+        <v>4.9942075397017276E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.0714615029967727E-2</v>
+        <v>5.0761421319796954E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4960,22 +4960,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5019,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5071,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5218,13 +5218,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5263,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5412,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5431,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8983532786438631</v>
+        <v>1.8983532786438633</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5779,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5822,13 +5822,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5836,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5875,6 +5875,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5891,17 +5902,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13448,20 +13448,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.0714615029967727E-2</v>
+        <v>5.0761421319796954E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.0714615029967727E-2</v>
+        <v>5.0761421319796954E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.9935454126325491E-2</v>
+        <v>5.9990770650669129E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.2272936837252186E-2</v>
+        <v>3.2302722658052604E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14647,50 +14647,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9896024612879862E-2</v>
+        <v>4.9942075397017276E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.4823551340283876E-2</v>
+        <v>5.4874149910971726E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.537190020249403E-2</v>
+        <v>5.542300486350233E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.185106540395564E-2</v>
+        <v>4.188969121420387E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.4381066861710908E-2</v>
+        <v>4.4422027698685265E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4773351878043764E-2</v>
+        <v>3.4805445419232542E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.2918116467796343E-2</v>
+        <v>4.2957727096746771E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.5147935623542778E-2</v>
+        <v>3.5180374881155642E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.4121798680525318E-2</v>
+        <v>3.4153290880507343E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.4928609864844029E-2</v>
+        <v>3.4960846699052466E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2407213009798173E-2</v>
+        <v>3.2437122758768915E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14704,43 +14704,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7832487530621118E-2</v>
+        <v>5.7885863153630458E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7676025724232569E-2</v>
+        <v>5.77292569431751E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1119321755156925E-2</v>
+        <v>5.1166501562960487E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6897067972260939E-2</v>
+        <v>4.6940350914551905E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7812725558010706E-2</v>
+        <v>3.7847624243343439E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4538834190555515E-2</v>
+        <v>4.4579940636508955E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5494152004211098E-2</v>
+        <v>3.5526910797016094E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9092052139321447E-2</v>
+        <v>2.9118902210516023E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1440689875554755E-2</v>
+        <v>3.1469707586561264E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8756148163973771E-2</v>
+        <v>2.8782688217655335E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18460,7 +18460,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.69</v>
+        <v>-21.67</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19239,7 +19239,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8983532786438631</v>
+        <v>1.8983532786438633</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19311,7 +19311,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.3864060260578226E-2</v>
+        <v>6.4207293080563721E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6ECEE7-08EF-4C00-962E-14A6F398532F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A70C93-3253-4E0F-8352-78F578C776F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2501,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3149,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3821,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3865,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3880,6 +3854,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4380,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4511,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,19 +4629,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>1545350950.0180476</v>
       </c>
@@ -4639,19 +4655,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>462652711</v>
       </c>
@@ -4664,7 +4680,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-490634169.24661446</v>
       </c>
@@ -4674,19 +4690,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4696,19 +4712,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4723,7 +4739,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-53103191</v>
       </c>
@@ -4738,7 +4754,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-53103191</v>
       </c>
@@ -4756,7 +4772,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-1078102.8016474061</v>
       </c>
@@ -4766,19 +4782,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-373061939.75451189</v>
       </c>
@@ -4788,19 +4804,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4810,28 +4826,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>1197782656</v>
       </c>
@@ -4844,7 +4860,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>1090126258.2152739</v>
       </c>
@@ -4883,10 +4899,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4908,11 +4924,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.3932476207375345</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.41423799416800827</v>
       </c>
@@ -4922,11 +4938,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.30212796693987309</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.31742662653511533</v>
       </c>
@@ -4936,11 +4952,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.2760688428830085</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.2760688428830085</v>
       </c>
@@ -4960,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,19 +5106,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>1232137409</v>
       </c>
@@ -5128,7 +5144,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>0.12757636177577109</v>
       </c>
@@ -5137,7 +5153,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>0.79731882844192148</v>
       </c>
@@ -5151,7 +5167,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>3986106600</v>
       </c>
@@ -5164,7 +5180,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>3438409570.5196743</v>
       </c>
@@ -5195,7 +5211,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>601196472.20000005</v>
       </c>
@@ -5218,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8983532786438633</v>
+        <v>1.8983532786438631</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5793,13 +5809,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5822,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6017,377 +6033,377 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>3912067946</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>3953761873</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>3442276658</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>3585982881</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>3097760404</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>3530148817</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>3170768175</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>2766461106</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>2349397869</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>2271278419</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>2022497629</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>2044370995</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>1859278213</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>1944558974</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>1759673042</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>1964870699</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>1823717021</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>1601141545</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>1217181691</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>1231847822</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>215939947</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>207397035</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>195156946</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>213185806</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>192953310</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>185898567</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>172963266</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>205630910</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>136851488</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>120069547</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>89269733</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>87498038</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>73672626</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>96781098</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>101231609</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>100438990</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>86961905</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>94773690</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>54486141</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>46321930</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334"/>
-      <c r="D8" s="334"/>
-      <c r="E8" s="334"/>
-      <c r="F8" s="334"/>
-      <c r="G8" s="334"/>
-      <c r="H8" s="334"/>
-      <c r="I8" s="334"/>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="C8" s="321"/>
+      <c r="D8" s="321"/>
+      <c r="E8" s="321"/>
+      <c r="F8" s="321"/>
+      <c r="G8" s="321"/>
+      <c r="H8" s="321"/>
+      <c r="I8" s="321"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>53103191</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>71173386</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>95605656</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>115890645</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>105753716</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>112756416</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>145025415</v>
       </c>
-      <c r="J12" s="334"/>
-      <c r="K12" s="334"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>44666271</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>31733562</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>52174747</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>33876650</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>19155473</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>4307482</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>4873611</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>421611829</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>420155428</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>376893525</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>341900302</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>278949056</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>328294411</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>260328417</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>213401798</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>231671396</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>210665216</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>1263521768</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>1260103397</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>1116852803</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>1024605179</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>826130846</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>973082586</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>775474748</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>635601938</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>686914877</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>628263122</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>1132694</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>902070</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>981992</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>811462</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>704543</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>655511</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>823429</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>795223</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>574487</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>664400</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6399,171 +6415,171 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>462652711</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>475220049</v>
       </c>
-      <c r="E19" s="334">
+      <c r="E19" s="321">
         <v>495414928</v>
       </c>
-      <c r="F19" s="334">
+      <c r="F19" s="321">
         <v>518843271</v>
       </c>
-      <c r="G19" s="334">
+      <c r="G19" s="321">
         <v>514548362</v>
       </c>
-      <c r="H19" s="334">
+      <c r="H19" s="321">
         <v>506465473</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="321">
         <v>461283106</v>
       </c>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>1796295378</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>1918660921</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>1824331237</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>1780173946</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>1406522534</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>1537171961</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>1444509542</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>1205496354</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>1115094373</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>1144557072</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-63639368</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-64835794</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-70210601</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-142527256</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-270895581</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-402194776</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-379835205</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-373540520</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-977214365</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-798541878</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-1858931831</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-1289833762</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-1265281759</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-531189995</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-505624628</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-473414072</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-1448089374</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-325459944</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-187105322</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>-663410674</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6603,186 +6619,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>228574200</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>258206405</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>377357021</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>368491616</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>440548083</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>421649740</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>325786547</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>299260334</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>144293862</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>141547001</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>30681363</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>32289866</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>32129347</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>32745245</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>33982961</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>32833169</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>29410625</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>25220478</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>22595729</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>23419985</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>2666283503</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>3177151047</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>3678311933</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>4088929705</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>4074330379</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>4229364458</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>4170411465</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>5196347300</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>5071716119</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>4567360550</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>9658038463</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>9703983988</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>9148978365</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>8636995082</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>8015792917</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>7573059434</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>6922316334</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>6469671997</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>6136754819</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>5651796449</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>4958355</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>3825661</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>3525797</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>3043805</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>2722343</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>2647800</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>2467743</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>2144314</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>1849091</v>
       </c>
-      <c r="L32" s="334">
+      <c r="L32" s="321">
         <v>1774604</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6809,47 +6825,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>3912067946</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>3953761873</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>3442276658</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>3585982881</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>3097760404</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>3530148817</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>3170768175</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>2766461106</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>2349397869</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>2271278419</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6858,47 +6874,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-2022497629</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-2044370995</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-1859278213</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-1944558974</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-1759673042</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-1964870699</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-1823717021</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-1601141545</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-1217181691</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-1231847822</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6907,47 +6923,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>1889570317</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>1909390878</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>1582998445</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>1641423907</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>1338087362</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>1565278118</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>1347051154</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>1165319561</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>1132216178</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>1039430597</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6956,47 +6972,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-215939947</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-207397035</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-195156946</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-213185806</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-192953310</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-185898567</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-172963266</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-205630910</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-136851488</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-120069547</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7005,47 +7021,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-89269733</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-87498038</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-73672626</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-96781098</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-101231609</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-100438990</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-86961905</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-94773690</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-54486141</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-46321930</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7054,47 +7070,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-126670214</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-119898997</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-121484320</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-116404708</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-91721701</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-85459577</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-86001361</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-110857220</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-82365347</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-73747617</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7103,47 +7119,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7152,47 +7168,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>1673630370</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>1701993843</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>1387841499</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>1428238101</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>1145134052</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>1379379551</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>1174087888</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>959688651</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>995364690</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>919361050</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7299,47 +7315,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-421611829</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-420155428</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-376893525</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-341900302</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-278949056</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-328294411</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-260328417</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-213401798</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-231671396</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-210665216</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7348,47 +7364,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>1263521768</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>1260103397</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>1116852803</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>1024605179</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>826130846</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>973082586</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>775474748</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>635601938</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>686914877</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>628263122</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7397,47 +7413,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-1132694</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>-902070</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>-981992</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>-811462</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>-704543</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>-655511</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>-823429</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>-795223</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>-574487</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-664400</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7451,47 +7467,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-53103191</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-71173386</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-95605656</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-115890645</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-105753716</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-112756416</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-145025415</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7500,47 +7516,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>44666271</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>31733562</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>52174747</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>33876650</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>19155473</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>4307482</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>4873611</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7756,47 +7772,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-462652711</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-475220049</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>-495414928</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>-518843271</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>-514548362</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>-506465473</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>-461283106</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7805,47 +7821,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-462652711</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-475220049</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-495414928</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-518843271</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-514548362</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>-506465473</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>-461283106</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7854,47 +7870,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7903,47 +7919,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-126275821</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>563991365</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>488838877</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>1106456695</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>630002325</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>661563113</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>-383415037</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>506495890</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>-49225314</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>-317395480</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8325,115 +8341,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>228574200</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>258206405</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>377357021</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>368491616</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>440548083</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>421649740</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>30681363</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>32289866</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>32129347</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>32745245</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>33982961</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>32833169</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>2666283503</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>3177151047</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>3678311933</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>4088929705</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>4074330379</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>4229364458</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>4170411465</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>5196347300</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>5071716119</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>4567360550</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8442,47 +8458,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>9658038463</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>9703983988</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>9148978365</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>8636995082</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>8015792917</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>7573059434</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>6922316334</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>6469671997</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>6136754819</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>5651796449</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9565,11 +9581,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-278870696.94999999</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-273848514.74016273</v>
       </c>
@@ -9597,8 +9613,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>547697029.48032546</v>
       </c>
@@ -9902,54 +9918,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:J4)</f>
         <v>3723522339.5</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>3912067946</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>3953761873</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>3442276658</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>3585982881</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>3097760404</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>3530148817</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>3170768175</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>2766461106</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>2349397869</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>2271278419</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9959,52 +9975,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-2057056829.7319524</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-2111767362</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-2131869033</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-1932950839</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-2041340072</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-1860904651</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-2065309689</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-1910678926</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-1695915235</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-1271667832</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-1278169752</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10014,52 +10030,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>1666465509.7680476</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>1800300584</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>1821892840</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>1509325819</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>1544642809</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>1236855753</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>1464839128</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>1260089249</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>1070545871</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>1077730037</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>993108667</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10069,52 +10085,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-121114559.75</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-126670214</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-119898997</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-121484320</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-116404708</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-91721701</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-85459577</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-86001361</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-110857220</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-82365347</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-73747617</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10124,54 +10140,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>1545350950.0180476</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>1673630370</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>1701993843</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>1387841499</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>1428238101</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>1145134052</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>1379379551</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>1174087888</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>959688651</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>995364690</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>919361050</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10181,52 +10197,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>462652711</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>462652711</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>475220049</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>495414928</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>518843271</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>514548362</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>506465473</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>461283106</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10236,52 +10252,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-490634169.24661446</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-462652711</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-475220049</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-495414928</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-518843271</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-514548362</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>-506465473</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>-461283106</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10291,54 +10307,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10348,52 +10364,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-53103191</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>-53103191</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>-71173386</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-95605656</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-115890645</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>-105753716</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-112756416</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-145025415</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10403,52 +10419,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>1464266300.7714331</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1620527179</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>1630820457</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>1292235843</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>1312347456</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>1039380336</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>1266623135</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>1029062473</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>959688651</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>995364690</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>919361050</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10458,52 +10474,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-373061939.75451189</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-421611829</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-420155428</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-376893525</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-341900302</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-278949056</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-328294411</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-260328417</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-213401798</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-231671396</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-210665216</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10513,54 +10529,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-1078102.8016474061</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-1132694</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>-902070</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>-981992</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>-811462</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>-704543</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>-655511</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>-823429</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>-795223</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>-574487</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-664400</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10570,54 +10586,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>1090126258.2152739</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>1197782656</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>1209762959</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>914360326</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>969635692</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>759726737</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>937673213</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>767910627</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>745491630</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>763118807</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>708031434</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10627,7 +10643,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10636,24 +10652,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10661,71 +10677,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>1090126258.2152739</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>1197782656</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>1209762959</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>914360326</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>969635692</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>759726737</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>937673213</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>767910627</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>745491630</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>763118807</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>708031434</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10798,54 +10814,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-1970168054.1106753</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-2022497629</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-2044370995</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-1859278213</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-1944558974</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-1759673042</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-1964870699</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-1823717021</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-1601141545</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-1217181691</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-1231847822</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10855,54 +10871,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-86888775.621277019</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-89269733</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-87498038</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-73672626</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-96781098</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-101231609</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-100438990</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-86961905</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-94773690</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-54486141</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-46321930</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10912,54 +10928,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-2057056829.7319524</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-2111767362</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-2131869033</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-1932950839</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-2041340072</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-1860904651</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-2065309689</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-1910678926</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-1695915235</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-1271667832</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-1278169752</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11165,54 +11181,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:J33)</f>
         <v>-121114559.75</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-126670214</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-119898997</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-121484320</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-116404708</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-91721701</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-85459577</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-86001361</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-110857220</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-82365347</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-73747617</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11222,7 +11238,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
@@ -11231,47 +11247,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>0</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>0</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>0</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11281,54 +11297,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-121114559.75</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-126670214</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-119898997</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-121484320</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-116404708</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-91721701</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-85459577</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-86001361</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-110857220</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-82365347</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-73747617</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11622,52 +11638,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-53103191</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-53103191</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-71173386</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-95605656</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-115890645</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-105753716</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-112756416</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-145025415</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11677,52 +11693,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11732,54 +11748,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>44666271</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>31733562</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>52174747</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>33876650</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>19155473</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>4307482</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>4873611</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11789,52 +11805,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-53103191</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-53103191</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>-71173386</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-95605656</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-115890645</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>-105753716</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-112756416</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-145025415</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11980,52 +11996,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12035,52 +12051,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12090,52 +12106,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12145,52 +12161,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12200,53 +12216,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>19940147</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>17704806</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>149335738</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>20281375</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>46544093</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>30446380</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>1867081</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-110684915</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>-76778417</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>-80432712</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12256,52 +12272,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>19940147</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>17704806</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>149335738</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>20281375</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>46544093</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>30446380</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>1867081</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-110684915</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>-76778417</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>-80432712</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13676,54 +13692,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>12324321966</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>12324321966</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>12881135035</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>12827290298</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>12725924787</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>12090123296</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>11802423892</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>11092727799</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>11666019297</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>11208470938</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>10219156999</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13733,54 +13749,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>228574200</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>258206405</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>377357021</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>368491616</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>440548083</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>421649740</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13790,54 +13806,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>30681363</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>32289866</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>32129347</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>32745245</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>33982961</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>32833169</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13847,54 +13863,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>2666283503</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>2666283503</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>3177151047</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>3678311933</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>4088929705</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>4074330379</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>4229364458</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>4170411465</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>5196347300</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>5071716119</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>4567360550</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13904,54 +13920,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>9658038463</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>9658038463</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>9703983988</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>9148978365</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>8636995082</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>8015792917</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>7573059434</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>6922316334</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>6469671997</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>6136754819</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>5651796449</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15449,7 +15465,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15488,7 +15504,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>1090126258.2152739</v>
       </c>
@@ -15520,7 +15536,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>18168770970.254566</v>
       </c>
@@ -15528,17 +15544,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>1232137409</v>
       </c>
@@ -15546,15 +15562,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>3438409570.5196743</v>
       </c>
@@ -15562,15 +15578,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>601196472.20000005</v>
       </c>
@@ -15578,15 +15594,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>20976239603.974239</v>
       </c>
@@ -15653,7 +15669,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15663,7 +15679,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15677,10 +15693,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15698,7 +15714,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15720,7 +15736,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15742,7 +15758,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15762,9 +15778,19 @@
         <f t="shared" si="1"/>
         <v>1036820695.8407583</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15784,9 +15810,19 @@
         <f t="shared" si="1"/>
         <v>1019637837.1791052</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15806,9 +15842,19 @@
         <f t="shared" si="1"/>
         <v>1002739743.8900673</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15830,7 +15876,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15852,7 +15898,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15874,7 +15920,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15896,7 +15942,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15918,7 +15964,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15940,7 +15986,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15962,11 +16008,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15982,13 +16028,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16004,13 +16060,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16026,9 +16092,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16050,7 +16126,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16072,7 +16148,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16094,7 +16170,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16116,7 +16192,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16138,7 +16214,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16160,7 +16236,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16182,7 +16258,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16204,7 +16280,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16226,7 +16302,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16248,7 +16324,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16270,11 +16346,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16290,13 +16366,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16312,13 +16398,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16334,13 +16430,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16356,9 +16462,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16380,7 +16496,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16391,11 +16507,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16405,7 +16521,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>20531263785.115143</v>
@@ -16432,7 +16548,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16454,7 +16570,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16475,14 +16591,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>18168770970.254551</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>19010101200.11388</v>
       </c>
       <c r="D58" s="123">
@@ -16494,16 +16610,26 @@
       <c r="F58" s="123">
         <v>24387958794.966114</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>18168770970.254551</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>19364349053.217316</v>
       </c>
       <c r="D59" s="123">
@@ -16515,16 +16641,26 @@
       <c r="F59" s="123">
         <v>27807540354.755692</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>18168770970.254551</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>19716333824.36945</v>
       </c>
       <c r="D60" s="123">
@@ -16536,16 +16672,26 @@
       <c r="F60" s="123">
         <v>31740453134.6306</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>18168770970.254547</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>20047897203.448524</v>
       </c>
       <c r="D61" s="123">
@@ -16557,26 +16703,56 @@
       <c r="F61" s="123">
         <v>36056956864.10157</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16948,6 +17124,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17050,7 +17296,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>18466846456.666668</v>
       </c>
@@ -17058,8 +17304,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18516,7 +18762,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>1673630370</v>
       </c>
@@ -18524,11 +18770,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国国贸(600007.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18541,7 +18787,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>1197782656</v>
       </c>
@@ -18549,8 +18795,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18563,7 +18809,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>1090126258.2152739</v>
       </c>
@@ -18571,8 +18817,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18582,8 +18828,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18596,8 +18842,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18615,8 +18861,8 @@
         <v>2.9436096404119594E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18633,8 +18879,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.4272741432500604E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18651,8 +18897,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>7.2975508413014145E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18678,21 +18924,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18706,8 +18952,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18721,8 +18967,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18742,8 +18988,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18753,8 +18999,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18768,8 +19014,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18779,8 +19025,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18800,8 +19046,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18811,8 +19057,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18826,8 +19072,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18837,8 +19083,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18858,8 +19104,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18869,8 +19115,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18884,8 +19130,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18896,8 +19142,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18959,8 +19205,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18970,8 +19216,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18985,8 +19231,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18996,8 +19242,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19017,8 +19263,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19028,8 +19274,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19043,8 +19289,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19054,8 +19300,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19239,7 +19485,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19248,7 +19494,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8983532786438633</v>
+        <v>1.8983532786438631</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A70C93-3253-4E0F-8352-78F578C776F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5BB5C4-9A02-442E-AFD5-C52288C57E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>21.67</v>
+        <v>21.62</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21827.812511780001</v>
+        <v>21777.448385080002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4396,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.4207293080563721E-2</v>
+        <v>6.5067285594782476E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4527,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.9942075397017276E-2</v>
+        <v>5.0057575108851261E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.0761421319796954E-2</v>
+        <v>5.0878815911193344E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8983532786438631</v>
+        <v>1.8983532786438633</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13464,20 +13464,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.0761421319796954E-2</v>
+        <v>5.0878815911193344E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.0761421319796954E-2</v>
+        <v>5.0878815911193344E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.9990770650669129E-2</v>
+        <v>6.0129509713228495E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.2302722658052604E-2</v>
+        <v>3.2377428307123028E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14663,50 +14663,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9942075397017276E-2</v>
+        <v>5.0057575108851261E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.4874149910971726E-2</v>
+        <v>5.5001055900590068E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.542300486350233E-2</v>
+        <v>5.555118017539757E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.188969121420387E-2</v>
+        <v>4.1986568390924968E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.4422027698685265E-2</v>
+        <v>4.452476134276178E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4805445419232542E-2</v>
+        <v>3.4885939048786736E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.2957727096746771E-2</v>
+        <v>4.3057074291697625E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.5180374881155642E-2</v>
+        <v>3.5261735600122239E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.4153290880507343E-2</v>
+        <v>3.4232276289574197E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.4960846699052466E-2</v>
+        <v>3.5041699721020676E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2437122758768915E-2</v>
+        <v>3.2512139231384019E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14720,43 +14720,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7885863153630458E-2</v>
+        <v>5.8019734252505652E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.77292569431751E-2</v>
+        <v>5.7862765863025183E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1166501562960487E-2</v>
+        <v>5.1284832972680564E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6940350914551905E-2</v>
+        <v>4.7048908617869561E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7847624243343439E-2</v>
+        <v>3.7935153439095849E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4579940636508955E-2</v>
+        <v>4.4683039481644274E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5526910797016094E-2</v>
+        <v>3.5609072940394948E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9118902210516023E-2</v>
+        <v>2.9186244722566246E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1469707586561264E-2</v>
+        <v>3.1542486743791981E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8782688217655335E-2</v>
+        <v>2.884925317653058E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18706,7 +18706,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.67</v>
+        <v>-21.62</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18946,7 +18946,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.67</v>
+        <v>21.62</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8983532786438631</v>
+        <v>1.8983532786438633</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.67</v>
+        <v>21.62</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19557,7 +19557,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.4207293080563721E-2</v>
+        <v>6.5067285594782476E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8CD5E6-2A5D-45C0-8B6D-7179480EC029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07391E1-D2CD-8B45-98A3-30A5AC15E9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,17 +4340,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.53</v>
+        <v>21.76</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4349,13 +4360,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21686.792957019999</v>
+        <v>21918.46793984</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4377,7 +4388,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4387,27 +4398,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4435,7 +4446,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4443,7 +4454,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4451,7 +4462,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4467,7 +4478,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4481,14 +4492,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.6622190545049031E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>6.2666166557424186E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4507,7 +4518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4523,10 +4534,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4545,7 +4556,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4564,7 +4575,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4583,11 +4594,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4597,25 +4608,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4624,16 +4635,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4646,20 +4657,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4672,7 +4683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4685,16 +4696,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4707,16 +4718,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4731,7 +4742,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4746,7 +4757,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4759,12 +4770,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4777,16 +4788,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4799,8 +4810,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4808,7 +4819,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4821,25 +4832,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4852,7 +4863,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4865,23 +4876,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.0266826467875725E-2</v>
+        <v>4.9735513504290646E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.1091500232234091E-2</v>
+        <v>5.0551470588235295E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4891,7 +4902,7 @@
         <v>1.0164059245889612</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4902,7 +4913,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4915,7 +4926,7 @@
         <v>0.16779050789746269</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4929,7 +4940,7 @@
         <v>0.41423799416800827</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4943,7 +4954,7 @@
         <v>0.31742662653511533</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4957,7 +4968,7 @@
         <v>1.2760688428830085</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4967,34 +4978,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5003,7 +5014,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5012,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5021,34 +5032,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5056,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5069,7 +5080,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5079,38 +5090,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5123,7 +5134,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5136,7 +5147,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5145,7 +5156,7 @@
         <v>0.12757636177577109</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5154,12 +5165,12 @@
         <v>0.79731882844192148</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5172,7 +5183,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5185,7 +5196,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5198,12 +5209,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5216,7 +5227,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5229,16 +5240,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5251,7 +5262,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5264,7 +5275,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5274,16 +5285,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5300,7 +5311,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5322,7 +5333,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5344,7 +5355,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5366,7 +5377,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5388,7 +5399,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5410,7 +5421,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5423,16 +5434,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5442,30 +5453,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5474,16 +5485,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5496,7 +5507,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5509,26 +5520,26 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8983532786438631</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+        <v>1.8983532786438633</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5538,7 +5549,7 @@
         <v>9.4567503881706401</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5551,7 +5562,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5573,12 +5584,12 @@
         <v>0.4975938398768166</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5587,7 +5598,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5597,7 +5608,7 @@
         <v>2.365137899745049</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5607,7 +5618,7 @@
         <v>13.514002373505772</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5620,7 +5631,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5633,7 +5644,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5642,12 +5653,12 @@
         <v>0.29742800023424332</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5656,7 +5667,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5666,7 +5677,7 @@
         <v>2.9403131444078037</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5676,7 +5687,7 @@
         <v>18.976606491350839</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5689,7 +5700,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5702,7 +5713,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5711,12 +5722,12 @@
         <v>3.0286665888368924E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5735,7 +5746,7 @@
         <v>2.7993790642942851</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5745,7 +5756,7 @@
         <v>17.597359866884187</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5758,7 +5769,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5771,7 +5782,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5780,7 +5791,7 @@
         <v>0.11969174215505141</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5790,21 +5801,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5813,80 +5824,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5925,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5944,15 +5955,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6001,7 +6012,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6017,7 +6028,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6025,7 +6036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6061,7 +6072,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6097,7 +6108,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6133,7 +6144,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6169,7 +6180,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6185,7 +6196,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6201,7 +6212,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6217,7 +6228,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6233,7 +6244,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6263,7 +6274,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6293,7 +6304,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6329,7 +6340,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6365,7 +6376,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6401,13 +6412,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6437,7 +6448,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6453,7 +6464,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6469,7 +6480,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6505,7 +6516,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6541,7 +6552,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6577,7 +6588,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6603,7 +6614,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6611,7 +6622,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6648,7 +6659,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6685,7 +6696,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6722,7 +6733,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6759,7 +6770,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6796,7 +6807,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6812,12 +6823,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6866,7 +6877,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6915,7 +6926,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6964,7 +6975,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7013,7 +7024,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7062,7 +7073,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7111,7 +7122,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7160,7 +7171,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7209,7 +7220,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7258,7 +7269,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7307,7 +7318,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7356,7 +7367,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7405,7 +7416,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7454,12 +7465,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7508,7 +7519,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7557,12 +7568,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7611,7 +7622,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7660,7 +7671,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7709,7 +7720,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7758,13 +7769,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7813,7 +7824,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7862,7 +7873,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7911,7 +7922,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7960,7 +7971,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8009,12 +8020,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8064,7 +8075,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8113,7 +8124,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8163,7 +8174,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8212,7 +8223,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8262,7 +8273,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8278,13 +8289,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8333,7 +8344,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8367,7 +8378,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8401,7 +8412,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8450,7 +8461,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8531,18 +8542,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8558,7 +8569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8569,7 +8580,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8589,7 +8600,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8611,7 +8622,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8632,7 +8643,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8653,7 +8664,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8674,7 +8685,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8695,7 +8706,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8716,7 +8727,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8728,7 +8739,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8740,7 +8751,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8764,12 +8775,12 @@
         <v>3587495939.0999999</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8789,7 +8800,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8809,7 +8820,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8829,7 +8840,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8849,7 +8860,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8869,7 +8880,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8890,7 +8901,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8910,7 +8921,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8930,7 +8941,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8942,7 +8953,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8955,7 +8966,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8979,7 +8990,7 @@
         <v>601196473.00000012</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -8996,7 +9007,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9015,7 +9026,7 @@
         <v>2595022082.4499998</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9030,7 +9041,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9049,7 +9060,7 @@
         <v>2590063727.4499998</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9065,7 +9076,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9082,7 +9093,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9102,7 +9113,7 @@
         <v>5261305585.4499998</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9113,7 +9124,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9126,7 +9137,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9145,7 +9156,7 @@
         <v>1072613173.35</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9161,7 +9172,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9177,7 +9188,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9193,7 +9204,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9212,7 +9223,7 @@
         <v>3504047.1</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9232,7 +9243,7 @@
         <v>4188692412.0999999</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9252,7 +9263,7 @@
         <v>3587495939.8999996</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9271,7 +9282,7 @@
         <v>601196472.20000005</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9282,7 +9293,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9296,7 +9307,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9310,7 +9321,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9325,10 +9336,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9341,7 +9352,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9355,7 +9366,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9366,10 +9377,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9381,7 +9392,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9395,7 +9406,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9409,10 +9420,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9424,7 +9435,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9435,7 +9446,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9446,10 +9457,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9461,7 +9472,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9477,7 +9488,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9488,7 +9499,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9502,7 +9513,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9518,7 +9529,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9528,7 +9539,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9538,7 +9549,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9548,7 +9559,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9558,10 +9569,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9573,7 +9584,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9589,7 +9600,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9605,7 +9616,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9618,7 +9629,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9631,10 +9642,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9646,7 +9657,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9660,7 +9671,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9674,7 +9685,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9688,7 +9699,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9702,7 +9713,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9713,7 +9724,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9721,7 +9732,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9738,7 +9749,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9755,7 +9766,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9772,7 +9783,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9803,19 +9814,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9872,7 +9883,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9895,7 +9906,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9909,7 +9920,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9966,7 +9977,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10021,7 +10032,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10076,7 +10087,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10131,7 +10142,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10188,7 +10199,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10243,7 +10254,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10298,7 +10309,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10355,7 +10366,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10410,7 +10421,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10465,7 +10476,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10520,7 +10531,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10577,7 +10588,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10634,7 +10645,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10660,7 +10671,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10685,7 +10696,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10742,7 +10753,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10761,7 +10772,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10784,7 +10795,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10805,7 +10816,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10862,7 +10873,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10919,7 +10930,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10976,18 +10987,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11046,7 +11057,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11106,7 +11117,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11161,18 +11172,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11229,7 +11240,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11288,7 +11299,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11345,18 +11356,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11414,7 +11425,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11472,7 +11483,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11527,18 +11538,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11596,10 +11607,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11622,14 +11633,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11684,7 +11695,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11739,7 +11750,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11796,7 +11807,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11851,11 +11862,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11865,7 +11876,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11891,7 +11902,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11918,7 +11929,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11973,11 +11984,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11987,7 +11998,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12042,7 +12053,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12097,7 +12108,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12152,7 +12163,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12207,7 +12218,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12263,7 +12274,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12318,11 +12329,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12332,7 +12343,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12357,7 +12368,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12382,7 +12393,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12407,7 +12418,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12434,10 +12445,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12460,7 +12471,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12481,7 +12492,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12538,7 +12549,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12595,7 +12606,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12652,7 +12663,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12709,7 +12720,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12766,7 +12777,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12825,7 +12836,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12882,7 +12893,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12939,7 +12950,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -12996,7 +13007,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13053,7 +13064,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13111,7 +13122,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13168,7 +13179,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13194,7 +13205,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13218,7 +13229,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13275,18 +13286,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13342,7 +13353,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13398,7 +13409,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13453,27 +13464,27 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.1091500232234091E-2</v>
+        <v>5.0551470588235295E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.1091500232234091E-2</v>
+        <v>5.0551470588235295E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.0380863910822105E-2</v>
+        <v>5.9742647058823525E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.2512772875058056E-2</v>
+        <v>3.216911764705882E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13508,11 +13519,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13533,7 +13544,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13590,7 +13601,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13647,10 +13658,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13673,7 +13684,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13683,7 +13694,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13740,7 +13751,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13797,7 +13808,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13854,7 +13865,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13911,7 +13922,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13968,11 +13979,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -13995,7 +14006,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14052,7 +14063,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14109,7 +14120,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14136,18 +14147,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14199,7 +14210,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14251,11 +14262,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14309,7 +14320,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14364,7 +14375,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14418,7 +14429,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14474,7 +14485,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14531,7 +14542,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14550,7 +14561,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14573,7 +14584,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14594,7 +14605,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14652,795 +14663,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0266826467875725E-2</v>
+        <v>4.9735513504290646E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.5230972065525186E-2</v>
+        <v>5.4647188812994359E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.5783395977338383E-2</v>
+        <v>5.5193773685298507E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.2162081217454614E-2</v>
+        <v>4.1716434219292178E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.4710884358128644E-2</v>
+        <v>4.4238296885593276E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.5031769727578689E-2</v>
+        <v>3.4661489073289024E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.3237062061611826E-2</v>
+        <v>4.2780052674012067E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.5409137188789727E-2</v>
+        <v>3.5034867815930279E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.4375374518374094E-2</v>
+        <v>3.4012031864917011E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.5188181512701672E-2</v>
+        <v>3.481624760884499E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2648046919764161E-2</v>
+        <v>3.2302961865005628E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.82622691379086E-2</v>
+        <v>5.7646445521101666E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8104644587022969E-2</v>
+        <v>5.7490487038538811E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1499214531786061E-2</v>
+        <v>5.0954875407598986E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7245583108143981E-2</v>
+        <v>4.6746204242570769E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8093730485520311E-2</v>
+        <v>3.7691085356307552E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4869824133448637E-2</v>
+        <v>4.4395556690861634E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5757926473355267E-2</v>
+        <v>3.5379970449050502E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9308249461304333E-2</v>
+        <v>2.8998465574535032E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1674341077602537E-2</v>
+        <v>3.1339547950403612E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8969849218606188E-2</v>
+        <v>2.8663642172637463E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15462,16 +15473,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15483,7 +15494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15496,7 +15507,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15517,7 +15528,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15528,7 +15539,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15546,7 +15557,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15562,7 +15573,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15578,7 +15589,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15594,7 +15605,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15608,7 +15619,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15622,7 +15633,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15636,10 +15647,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15649,13 +15660,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15665,7 +15676,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15675,7 +15686,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15689,10 +15700,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15710,7 +15721,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15732,7 +15743,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15754,7 +15765,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15786,7 +15797,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15818,7 +15829,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15850,7 +15861,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15872,7 +15883,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15894,7 +15905,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15916,7 +15927,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15938,7 +15949,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15960,7 +15971,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15982,7 +15993,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16004,7 +16015,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16036,7 +16047,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16068,7 +16079,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16100,7 +16111,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16122,7 +16133,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16144,7 +16155,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16166,7 +16177,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16188,7 +16199,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16210,7 +16221,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16232,7 +16243,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16254,7 +16265,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16276,7 +16287,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16298,7 +16309,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16320,7 +16331,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16342,7 +16353,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16374,7 +16385,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16406,7 +16417,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16438,7 +16449,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16470,7 +16481,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16492,7 +16503,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16503,11 +16514,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16517,7 +16528,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>20531263785.115143</v>
@@ -16544,7 +16555,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16566,7 +16577,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16587,7 +16598,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16618,7 +16629,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16649,7 +16660,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16680,7 +16691,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16711,7 +16722,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16728,7 +16739,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16748,7 +16759,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16771,7 +16782,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16797,7 +16808,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16824,7 +16835,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16851,7 +16862,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16878,7 +16889,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16905,7 +16916,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16931,7 +16942,7 @@
         <v>34.298144365868922</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16957,7 +16968,7 @@
         <v>38.583440282129665</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16974,7 +16985,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16996,7 +17007,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17019,7 +17030,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17042,7 +17053,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17065,7 +17076,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17087,14 +17098,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17102,26 +17113,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17135,7 +17146,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17149,7 +17160,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17163,7 +17174,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17177,7 +17188,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17222,16 +17233,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17243,7 +17254,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17256,7 +17267,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17277,7 +17288,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17288,7 +17299,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17304,7 +17315,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17318,10 +17329,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17331,13 +17342,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17347,7 +17358,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17357,7 +17368,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17371,10 +17382,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17392,7 +17403,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17414,7 +17425,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17436,7 +17447,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17458,7 +17469,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17480,7 +17491,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17502,7 +17513,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17524,7 +17535,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17546,7 +17557,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17568,7 +17579,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17590,7 +17601,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17612,7 +17623,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17634,7 +17645,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17656,7 +17667,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17678,7 +17689,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17700,7 +17711,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17722,7 +17733,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17744,7 +17755,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17766,7 +17777,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17788,7 +17799,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17810,7 +17821,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17832,7 +17843,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17854,7 +17865,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17876,7 +17887,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17898,7 +17909,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17920,7 +17931,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17942,7 +17953,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17964,7 +17975,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17986,7 +17997,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18008,7 +18019,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18030,7 +18041,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18052,7 +18063,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18074,7 +18085,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18085,11 +18096,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18099,7 +18110,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>20868098150.489811</v>
@@ -18126,7 +18137,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18148,7 +18159,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18169,7 +18180,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18190,7 +18201,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18211,7 +18222,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18232,7 +18243,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18253,14 +18264,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18270,7 +18281,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18293,7 +18304,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18319,7 +18330,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18346,7 +18357,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18373,7 +18384,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18400,7 +18411,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18427,7 +18438,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18453,7 +18464,7 @@
         <v>32.027940052792374</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18479,7 +18490,7 @@
         <v>36.383540210696673</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18496,7 +18507,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18518,7 +18529,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18541,7 +18552,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18564,7 +18575,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18587,7 +18598,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18609,14 +18620,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18624,23 +18635,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18670,17 +18681,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18693,7 +18704,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18702,10 +18713,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.53</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-21.76</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18725,7 +18736,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18734,7 +18745,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18754,7 +18765,7 @@
         <v>23.70144195690272</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18779,7 +18790,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18801,7 +18812,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18823,7 +18834,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18834,7 +18845,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18848,7 +18859,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18867,7 +18878,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18885,7 +18896,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18896,7 +18907,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18905,7 +18916,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18913,7 +18924,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18925,24 +18936,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.53</v>
+        <v>21.76</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18951,7 +18962,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18966,7 +18977,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18975,7 +18986,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18987,7 +18998,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -18998,7 +19009,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19013,7 +19024,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19024,7 +19035,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19033,7 +19044,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19045,7 +19056,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19056,7 +19067,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19071,7 +19082,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19082,7 +19093,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19091,7 +19102,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19103,7 +19114,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19114,7 +19125,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19129,7 +19140,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19141,7 +19152,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19154,7 +19165,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19163,12 +19174,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19178,12 +19189,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19192,7 +19203,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19204,7 +19215,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19215,7 +19226,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19230,7 +19241,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19241,7 +19252,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19250,7 +19261,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19262,7 +19273,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19273,7 +19284,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19288,7 +19299,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19299,7 +19310,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19319,7 +19330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19328,7 +19339,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19336,7 +19347,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19349,7 +19360,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19361,7 +19372,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19377,7 +19388,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19385,7 +19396,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19395,7 +19406,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19407,7 +19418,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19417,7 +19428,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19433,7 +19444,7 @@
         <v>0.12331828082950577</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19442,12 +19453,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19457,7 +19468,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19470,33 +19481,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8983532786438631</v>
+        <v>1.8983532786438633</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19506,7 +19517,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19526,45 +19537,45 @@
         <v>0.4975938398768166</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.53</v>
+        <v>21.76</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.6622190545049031E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>6.2666166557424186E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19573,7 +19584,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19585,7 +19596,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19595,7 +19606,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19615,14 +19626,14 @@
         <v>0.29742800023424332</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19633,7 +19644,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19645,7 +19656,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19657,7 +19668,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19676,15 +19687,15 @@
         <v>3.0286665888368924E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19693,7 +19704,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19703,7 +19714,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19713,7 +19724,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19732,16 +19743,16 @@
         <v>0.11969174215505141</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19749,7 +19760,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19757,7 +19768,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07391E1-D2CD-8B45-98A3-30A5AC15E9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C88FD7-AC60-4FC4-815E-2E3B8E1C9EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2513,7 +2502,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3905,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3943,7 +3932,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4232,7 +4221,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4241,7 +4230,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4272,7 +4261,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4281,7 +4270,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +4287,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4308,7 +4297,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4318,17 +4307,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4340,17 +4329,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.76</v>
+        <v>22</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4360,13 +4349,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21918.46793984</v>
+        <v>22160.215747999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4388,7 +4377,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4398,27 +4387,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4433,7 +4422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4446,7 +4435,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4454,7 +4443,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4462,7 +4451,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4478,7 +4467,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4492,14 +4481,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.2666166557424186E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>5.8599020191868245E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4518,7 +4507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4537,7 +4526,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4556,7 +4545,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4575,7 +4564,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4594,11 +4583,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4608,25 +4597,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4635,16 +4624,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4657,20 +4646,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4683,7 +4672,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4696,16 +4685,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4718,16 +4707,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4742,7 +4731,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4757,7 +4746,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4770,12 +4759,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4788,16 +4777,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4810,8 +4799,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,7 +4808,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4832,25 +4821,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4863,7 +4852,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4876,23 +4865,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.9735513504290646E-2</v>
+        <v>4.9192944266062022E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.0551470588235295E-2</v>
+        <v>0.05</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4902,7 +4891,7 @@
         <v>1.0164059245889612</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4913,7 +4902,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4926,7 +4915,7 @@
         <v>0.16779050789746269</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4940,7 +4929,7 @@
         <v>0.41423799416800827</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4954,7 +4943,7 @@
         <v>0.31742662653511533</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4968,7 +4957,7 @@
         <v>1.2760688428830085</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4978,34 +4967,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5014,7 +5003,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5023,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5032,34 +5021,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5067,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5080,7 +5069,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5090,38 +5079,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5134,7 +5123,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5147,7 +5136,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5156,7 +5145,7 @@
         <v>0.12757636177577109</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5165,12 +5154,12 @@
         <v>0.79731882844192148</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5183,7 +5172,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5196,7 +5185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5209,12 +5198,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5227,7 +5216,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5240,16 +5229,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5262,7 +5251,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5275,7 +5264,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5285,16 +5274,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5311,7 +5300,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5333,7 +5322,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5355,7 +5344,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5377,7 +5366,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5399,7 +5388,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5421,7 +5410,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5434,16 +5423,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5453,30 +5442,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5485,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5494,7 +5483,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5507,7 +5496,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5520,7 +5509,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5529,7 +5518,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5539,7 +5528,7 @@
         <v>1.8983532786438633</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5549,7 +5538,7 @@
         <v>9.4567503881706401</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5562,7 +5551,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5584,12 +5573,12 @@
         <v>0.4975938398768166</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5598,7 +5587,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5608,7 +5597,7 @@
         <v>2.365137899745049</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5618,7 +5607,7 @@
         <v>13.514002373505772</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5631,7 +5620,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5644,7 +5633,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5653,12 +5642,12 @@
         <v>0.29742800023424332</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5667,7 +5656,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5677,7 +5666,7 @@
         <v>2.9403131444078037</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5687,7 +5676,7 @@
         <v>18.976606491350839</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5700,7 +5689,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5713,7 +5702,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5722,12 +5711,12 @@
         <v>3.0286665888368924E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5736,7 +5725,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5746,7 +5735,7 @@
         <v>2.7993790642942851</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5756,7 +5745,7 @@
         <v>17.597359866884187</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5769,7 +5758,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5782,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5791,7 +5780,7 @@
         <v>0.11969174215505141</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5801,21 +5790,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5824,91 +5813,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5925,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5955,15 +5944,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6012,7 +6001,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6028,7 +6017,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6036,7 +6025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6072,7 +6061,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6108,7 +6097,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6144,7 +6133,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6180,7 +6169,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6196,7 +6185,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6212,7 +6201,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6228,7 +6217,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6244,7 +6233,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6274,7 +6263,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6304,7 +6293,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6340,7 +6329,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6376,7 +6365,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6412,13 +6401,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6448,7 +6437,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6464,7 +6453,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6480,7 +6469,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6516,7 +6505,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6552,7 +6541,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6588,7 +6577,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6614,7 +6603,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6622,7 +6611,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6659,7 +6648,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6696,7 +6685,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6733,7 +6722,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6770,7 +6759,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6807,7 +6796,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6823,12 +6812,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6877,7 +6866,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6926,7 +6915,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6975,7 +6964,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7024,7 +7013,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7073,7 +7062,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7122,7 +7111,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7171,7 +7160,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7220,7 +7209,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7269,7 +7258,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7318,7 +7307,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7367,7 +7356,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7416,7 +7405,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7465,12 +7454,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7519,7 +7508,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7568,12 +7557,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7622,7 +7611,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7671,7 +7660,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7720,7 +7709,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7769,13 +7758,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7824,7 +7813,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7873,7 +7862,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7922,7 +7911,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7971,7 +7960,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8020,12 +8009,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8075,7 +8064,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8124,7 +8113,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8174,7 +8163,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8223,7 +8212,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8273,7 +8262,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8289,13 +8278,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8344,7 +8333,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8378,7 +8367,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8412,7 +8401,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8461,7 +8450,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8542,7 +8531,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8553,7 +8542,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8569,7 +8558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8580,7 +8569,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8600,7 +8589,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8622,7 +8611,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8643,7 +8632,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8664,7 +8653,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8685,7 +8674,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8706,7 +8695,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8727,7 +8716,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8739,7 +8728,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8751,7 +8740,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8775,12 +8764,12 @@
         <v>3587495939.0999999</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8800,7 +8789,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8820,7 +8809,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8840,7 +8829,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8860,7 +8849,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8880,7 +8869,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8901,7 +8890,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8921,7 +8910,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8941,7 +8930,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8953,7 +8942,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8966,7 +8955,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8990,7 +8979,7 @@
         <v>601196473.00000012</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9007,7 +8996,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9026,7 +9015,7 @@
         <v>2595022082.4499998</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9041,7 +9030,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9060,7 +9049,7 @@
         <v>2590063727.4499998</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9076,7 +9065,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9093,7 +9082,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9113,7 +9102,7 @@
         <v>5261305585.4499998</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9124,7 +9113,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9137,7 +9126,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9156,7 +9145,7 @@
         <v>1072613173.35</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9172,7 +9161,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9188,7 +9177,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9204,7 +9193,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9223,7 +9212,7 @@
         <v>3504047.1</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9243,7 +9232,7 @@
         <v>4188692412.0999999</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9263,7 +9252,7 @@
         <v>3587495939.8999996</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9282,7 +9271,7 @@
         <v>601196472.20000005</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9293,7 +9282,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9307,7 +9296,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9321,7 +9310,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9336,10 +9325,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9352,7 +9341,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9366,7 +9355,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9377,10 +9366,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9392,7 +9381,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9406,7 +9395,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9420,10 +9409,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9435,7 +9424,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9446,7 +9435,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9457,10 +9446,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9472,7 +9461,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9488,7 +9477,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9499,7 +9488,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9513,7 +9502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9529,7 +9518,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9539,7 +9528,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9549,7 +9538,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9559,7 +9548,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9569,10 +9558,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9584,7 +9573,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9600,7 +9589,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9616,7 +9605,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9629,7 +9618,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9642,10 +9631,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9657,7 +9646,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9671,7 +9660,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9685,7 +9674,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9699,7 +9688,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9713,7 +9702,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9724,7 +9713,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9732,7 +9721,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9749,7 +9738,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9766,7 +9755,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9783,7 +9772,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9814,19 +9803,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9883,7 +9872,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9906,7 +9895,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9920,7 +9909,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9977,7 +9966,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10032,7 +10021,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10087,7 +10076,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10142,7 +10131,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10199,7 +10188,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10254,7 +10243,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10309,7 +10298,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10366,7 +10355,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10421,7 +10410,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10476,7 +10465,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10531,7 +10520,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10588,7 +10577,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10645,7 +10634,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10671,7 +10660,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10696,7 +10685,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10753,7 +10742,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10772,7 +10761,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10795,7 +10784,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10816,7 +10805,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10873,7 +10862,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10930,7 +10919,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10987,18 +10976,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11057,7 +11046,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11117,7 +11106,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11172,18 +11161,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11240,7 +11229,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11299,7 +11288,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11356,18 +11345,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11425,7 +11414,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11483,7 +11472,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11538,18 +11527,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11607,10 +11596,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11633,14 +11622,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11695,7 +11684,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11750,7 +11739,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11807,7 +11796,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11862,11 +11851,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11876,7 +11865,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11902,7 +11891,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11929,7 +11918,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11984,11 +11973,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11998,7 +11987,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12053,7 +12042,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12108,7 +12097,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12163,7 +12152,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12218,7 +12207,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12274,7 +12263,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12329,11 +12318,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12343,7 +12332,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12368,7 +12357,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12393,7 +12382,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12418,7 +12407,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12445,10 +12434,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12471,7 +12460,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12492,7 +12481,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12549,7 +12538,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12606,7 +12595,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12663,7 +12652,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12720,7 +12709,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12777,7 +12766,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12836,7 +12825,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12893,7 +12882,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12950,7 +12939,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13007,7 +12996,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13064,7 +13053,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13122,7 +13111,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13179,7 +13168,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13205,7 +13194,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13229,7 +13218,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13286,18 +13275,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13353,7 +13342,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13409,7 +13398,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13464,27 +13453,27 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.0551470588235295E-2</v>
+        <v>0.05</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.0551470588235295E-2</v>
+        <v>0.05</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.9742647058823525E-2</v>
+        <v>5.909090909090909E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.216911764705882E-2</v>
+        <v>3.1818181818181815E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13519,11 +13508,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13544,7 +13533,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13601,7 +13590,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13658,10 +13647,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13684,7 +13673,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13694,7 +13683,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13751,7 +13740,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13808,7 +13797,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13865,7 +13854,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13922,7 +13911,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13979,11 +13968,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14006,7 +13995,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14063,7 +14052,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14120,7 +14109,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14147,18 +14136,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14210,7 +14199,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14262,11 +14251,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14320,7 +14309,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14375,7 +14364,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14429,7 +14418,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14485,7 +14474,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14542,7 +14531,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14561,7 +14550,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14584,7 +14573,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14605,7 +14594,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14663,795 +14652,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9735513504290646E-2</v>
+        <v>4.9192944266062022E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.4647188812994359E-2</v>
+        <v>5.405103766230715E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.5193773685298507E-2</v>
+        <v>5.45916597905498E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.1716434219292178E-2</v>
+        <v>4.126134584599081E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.4238296885593276E-2</v>
+        <v>4.375569728320499E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4661489073289024E-2</v>
+        <v>3.4283363737944057E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.2780052674012067E-2</v>
+        <v>4.2313361190295579E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.5034867815930279E-2</v>
+        <v>3.4652669257938314E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.4012031864917011E-2</v>
+        <v>3.364099151729974E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.481624760884499E-2</v>
+        <v>3.4436433998566683E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2302961865005628E-2</v>
+        <v>3.1950565917387382E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7646445521101666E-2</v>
+        <v>5.7017575206326013E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7490487038538811E-2</v>
+        <v>5.6863318089027476E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0954875407598986E-2</v>
+        <v>5.0399004039516089E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6746204242570769E-2</v>
+        <v>4.6236245650833632E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7691085356307552E-2</v>
+        <v>3.727990987969329E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4395556690861634E-2</v>
+        <v>4.3911241526961325E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5379970449050502E-2</v>
+        <v>3.4994007135060859E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8998465574535032E-2</v>
+        <v>2.8682118677358284E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1339547950403612E-2</v>
+        <v>3.0997661972762849E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8663642172637463E-2</v>
+        <v>2.8350947894390507E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15473,16 +15462,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15494,7 +15483,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15507,7 +15496,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15528,7 +15517,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15539,7 +15528,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15557,7 +15546,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15573,7 +15562,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15589,7 +15578,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15605,7 +15594,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15619,7 +15608,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15633,7 +15622,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15647,10 +15636,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15660,13 +15649,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15676,7 +15665,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15686,7 +15675,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15700,10 +15689,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15721,7 +15710,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15743,7 +15732,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15765,7 +15754,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15797,7 +15786,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15829,7 +15818,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15861,7 +15850,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15883,7 +15872,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15905,7 +15894,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15927,7 +15916,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15949,7 +15938,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15971,7 +15960,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15993,7 +15982,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16015,7 +16004,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16047,7 +16036,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16079,7 +16068,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16111,7 +16100,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16133,7 +16122,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16155,7 +16144,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16177,7 +16166,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16199,7 +16188,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16221,7 +16210,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16243,7 +16232,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16265,7 +16254,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16287,7 +16276,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16309,7 +16298,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16331,7 +16320,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16353,7 +16342,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16385,7 +16374,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16417,7 +16406,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16449,7 +16438,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16481,7 +16470,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16503,7 +16492,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16514,11 +16503,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16528,7 +16517,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>20531263785.115143</v>
@@ -16555,7 +16544,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16577,7 +16566,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16598,7 +16587,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16629,7 +16618,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16660,7 +16649,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16691,7 +16680,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16722,7 +16711,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16739,7 +16728,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16759,7 +16748,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16782,7 +16771,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16808,7 +16797,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16835,7 +16824,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16862,7 +16851,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16889,7 +16878,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16916,7 +16905,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16942,7 +16931,7 @@
         <v>34.298144365868922</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16968,7 +16957,7 @@
         <v>38.583440282129665</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16985,7 +16974,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17007,7 +16996,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17030,7 +17019,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17053,7 +17042,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17076,7 +17065,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17098,14 +17087,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17113,26 +17102,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17146,7 +17135,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17160,7 +17149,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17174,7 +17163,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17188,7 +17177,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17233,16 +17222,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17254,7 +17243,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17267,7 +17256,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17288,7 +17277,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17299,7 +17288,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17315,7 +17304,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17329,10 +17318,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17342,13 +17331,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17358,7 +17347,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17368,7 +17357,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17382,10 +17371,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17403,7 +17392,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17425,7 +17414,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17447,7 +17436,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17469,7 +17458,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17491,7 +17480,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17513,7 +17502,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17535,7 +17524,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17557,7 +17546,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17579,7 +17568,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17601,7 +17590,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17623,7 +17612,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17645,7 +17634,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17667,7 +17656,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17689,7 +17678,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17711,7 +17700,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17733,7 +17722,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17755,7 +17744,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17777,7 +17766,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17799,7 +17788,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17821,7 +17810,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17843,7 +17832,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17865,7 +17854,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17887,7 +17876,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17909,7 +17898,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17931,7 +17920,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17953,7 +17942,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17975,7 +17964,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17997,7 +17986,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18019,7 +18008,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18041,7 +18030,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18063,7 +18052,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18085,7 +18074,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18096,11 +18085,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18110,7 +18099,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>20868098150.489811</v>
@@ -18137,7 +18126,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18159,7 +18148,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18180,7 +18169,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18201,7 +18190,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18222,7 +18211,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18243,7 +18232,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18264,14 +18253,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18281,7 +18270,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18304,7 +18293,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18330,7 +18319,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18357,7 +18346,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18384,7 +18373,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18411,7 +18400,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18438,7 +18427,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18464,7 +18453,7 @@
         <v>32.027940052792374</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18490,7 +18479,7 @@
         <v>36.383540210696673</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18507,7 +18496,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18529,7 +18518,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18552,7 +18541,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18575,7 +18564,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18598,7 +18587,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18620,14 +18609,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18635,23 +18624,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18681,7 +18670,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18691,7 +18680,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18704,7 +18693,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18713,10 +18702,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.76</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18736,7 +18725,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18745,7 +18734,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18765,7 +18754,7 @@
         <v>23.70144195690272</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18790,7 +18779,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18812,7 +18801,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18834,7 +18823,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18845,7 +18834,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18859,7 +18848,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18878,7 +18867,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18896,7 +18885,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18907,7 +18896,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18916,7 +18905,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18924,7 +18913,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18936,24 +18925,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.76</v>
+        <v>22</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18962,7 +18951,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18977,7 +18966,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18986,7 +18975,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18998,7 +18987,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19009,7 +18998,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19024,7 +19013,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19035,7 +19024,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19044,7 +19033,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19056,7 +19045,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19067,7 +19056,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19082,7 +19071,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19093,7 +19082,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19102,7 +19091,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19114,7 +19103,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19125,7 +19114,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19140,7 +19129,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19152,7 +19141,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19165,7 +19154,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19174,12 +19163,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19189,12 +19178,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19203,7 +19192,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19215,7 +19204,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19226,7 +19215,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19241,7 +19230,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19252,7 +19241,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19261,7 +19250,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19273,7 +19262,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19284,7 +19273,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19299,7 +19288,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19310,7 +19299,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19330,7 +19319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19339,7 +19328,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19347,7 +19336,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19360,7 +19349,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19372,7 +19361,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19388,7 +19377,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19396,7 +19385,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19406,7 +19395,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19418,7 +19407,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19428,7 +19417,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19444,7 +19433,7 @@
         <v>0.12331828082950577</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19453,12 +19442,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19468,7 +19457,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19481,12 +19470,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19495,7 +19484,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19507,7 +19496,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19517,7 +19506,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19537,45 +19526,45 @@
         <v>0.4975938398768166</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.76</v>
+        <v>22</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.2666166557424186E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>5.8599020191868245E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19584,7 +19573,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19596,7 +19585,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19606,7 +19595,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19626,14 +19615,14 @@
         <v>0.29742800023424332</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19644,7 +19633,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19656,7 +19645,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19668,7 +19657,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19687,15 +19676,15 @@
         <v>3.0286665888368924E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19704,7 +19693,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19714,7 +19703,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19724,7 +19713,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19743,16 +19732,16 @@
         <v>0.11969174215505141</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19760,7 +19749,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19768,7 +19757,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C88FD7-AC60-4FC4-815E-2E3B8E1C9EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACD985C-6BB6-4154-BFDB-8F41076BA47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22</v>
+        <v>21.64</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22160.215747999999</v>
+        <v>21797.594035760001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.8599020191868245E-2</v>
+        <v>6.4722960477115787E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.9192944266062022E-2</v>
+        <v>5.0011311176218314E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0.05</v>
+        <v>5.083179297597043E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13460,20 +13460,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0.05</v>
+        <v>5.083179297597043E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0.05</v>
+        <v>5.083179297597043E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.909090909090909E-2</v>
+        <v>6.007393715341959E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.1818181818181815E-2</v>
+        <v>3.2347504621072089E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14659,50 +14659,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9192944266062022E-2</v>
+        <v>5.0011311176218314E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.405103766230715E-2</v>
+        <v>5.4950223131735552E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.45916597905498E-2</v>
+        <v>5.5499838973756724E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.126134584599081E-2</v>
+        <v>4.1947763799066444E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.375569728320499E-2</v>
+        <v>4.4483610916382151E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4283363737944057E-2</v>
+        <v>3.4853696960941274E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.2313361190295579E-2</v>
+        <v>4.3017280322851327E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.4652669257938314E-2</v>
+        <v>3.5229146195685901E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.364099151729974E-2</v>
+        <v>3.4200638326275151E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.4436433998566683E-2</v>
+        <v>3.5009313676916218E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.1950565917387382E-2</v>
+        <v>3.2482091043554644E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14716,43 +14716,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7017575206326013E-2</v>
+        <v>5.7966111577595757E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6863318089027476E-2</v>
+        <v>5.7809288260563974E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0399004039516089E-2</v>
+        <v>5.1237434790635576E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6236245650833632E-2</v>
+        <v>4.7005425338185761E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.727990987969329E-2</v>
+        <v>3.7900093223348072E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3911241526961325E-2</v>
+        <v>4.4641742772326673E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4994007135060859E-2</v>
+        <v>3.5576162521780905E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8682118677358284E-2</v>
+        <v>2.9159270374393819E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0997661972762849E-2</v>
+        <v>3.1513334722771839E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8350947894390507E-2</v>
+        <v>2.8822590280803657E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22</v>
+        <v>-21.64</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22</v>
+        <v>21.64</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22</v>
+        <v>21.64</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.8599020191868245E-2</v>
+        <v>6.4722960477115787E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACD985C-6BB6-4154-BFDB-8F41076BA47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922FD4AB-EDD2-4A5A-B298-95541A7987B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.64</v>
+        <v>21.56</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21797.594035760001</v>
+        <v>21717.011433039996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.4722960477115787E-2</v>
+        <v>6.610289652545509E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.0011311176218314E-2</v>
+        <v>5.0196881904144924E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.083179297597043E-2</v>
+        <v>5.1020408163265314E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13460,20 +13460,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.083179297597043E-2</v>
+        <v>5.1020408163265314E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.083179297597043E-2</v>
+        <v>5.1020408163265314E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.007393715341959E-2</v>
+        <v>6.0296846011131729E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.2347504621072089E-2</v>
+        <v>3.2467532467532464E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14659,50 +14659,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0011311176218314E-2</v>
+        <v>5.0196881904144924E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.4950223131735552E-2</v>
+        <v>5.5154120063578733E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.5499838973756724E-2</v>
+        <v>5.5705775296479389E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.1947763799066444E-2</v>
+        <v>4.2103414128562056E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.4483610916382151E-2</v>
+        <v>4.4648670697147952E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4853696960941274E-2</v>
+        <v>3.4983024222391898E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.3017280322851327E-2</v>
+        <v>4.3176899173770995E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.5229146195685901E-2</v>
+        <v>3.5359866589732974E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.4200638326275151E-2</v>
+        <v>3.4327542364591568E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.5009313676916218E-2</v>
+        <v>3.5139218365884371E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2482091043554644E-2</v>
+        <v>3.2602618283048355E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14716,43 +14716,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7966111577595757E-2</v>
+        <v>5.8181199190128589E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7809288260563974E-2</v>
+        <v>5.8023793968395396E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1237434790635576E-2</v>
+        <v>5.1427555142363364E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7005425338185761E-2</v>
+        <v>4.7179842500850652E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7900093223348072E-2</v>
+        <v>3.8040724367033971E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4641742772326673E-2</v>
+        <v>4.4807389313225851E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5576162521780905E-2</v>
+        <v>3.5708170545980474E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9159270374393819E-2</v>
+        <v>2.9267468038120702E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1513334722771839E-2</v>
+        <v>3.1630267319145769E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8822590280803657E-2</v>
+        <v>2.8929538667745423E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.64</v>
+        <v>-21.56</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.64</v>
+        <v>21.56</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.64</v>
+        <v>21.56</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.4722960477115787E-2</v>
+        <v>6.610289652545509E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922FD4AB-EDD2-4A5A-B298-95541A7987B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E62042D-4C72-4D15-9DE5-323BAD0B06BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E62042D-4C72-4D15-9DE5-323BAD0B06BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D493D2-02C4-42B3-BADC-A72C80661958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.56</v>
+        <v>22.05</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21717.011433039996</v>
+        <v>22210.579874700001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.610289652545509E-2</v>
+        <v>5.775937618961291E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.0196881904144924E-2</v>
+        <v>4.9081395639608359E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>5.1020408163265314E-2</v>
+        <v>4.9886621315192746E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13460,20 +13460,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>5.1020408163265314E-2</v>
+        <v>4.9886621315192746E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.1020408163265314E-2</v>
+        <v>4.9886621315192746E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.0296846011131729E-2</v>
+        <v>5.8956916099773243E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.2467532467532464E-2</v>
+        <v>3.1746031746031744E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14659,50 +14659,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0196881904144924E-2</v>
+        <v>4.9081395639608359E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.5154120063578733E-2</v>
+        <v>5.3928472951054754E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.5705775296479389E-2</v>
+        <v>5.446786917877984E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.2103414128562056E-2</v>
+        <v>4.1167782703482897E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.4648670697147952E-2</v>
+        <v>4.3656478014989099E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4983024222391898E-2</v>
+        <v>3.4205623684116518E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.3176899173770995E-2</v>
+        <v>4.2217412525464973E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.5359866589732974E-2</v>
+        <v>3.4574091776627791E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.4327542364591568E-2</v>
+        <v>3.3564708089822863E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.5139218365884371E-2</v>
+        <v>3.4358346846642497E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2602618283048355E-2</v>
+        <v>3.1878115654536167E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14716,43 +14716,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8181199190128589E-2</v>
+        <v>5.6888283652570169E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8023793968395396E-2</v>
+        <v>5.6734376324653266E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1427555142363364E-2</v>
+        <v>5.0284720583644166E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7179842500850652E-2</v>
+        <v>4.61314015563873E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8040724367033971E-2</v>
+        <v>3.7195374936655437E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4807389313225851E-2</v>
+        <v>4.3811669550709711E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5708170545980474E-2</v>
+        <v>3.491465564495868E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9267468038120702E-2</v>
+        <v>2.8617079859495794E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1630267319145769E-2</v>
+        <v>3.0927372489831413E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8929538667745423E-2</v>
+        <v>2.8286660030684408E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.56</v>
+        <v>-22.05</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.56</v>
+        <v>22.05</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.56</v>
+        <v>22.05</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.610289652545509E-2</v>
+        <v>5.775937618961291E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D493D2-02C4-42B3-BADC-A72C80661958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07967095-2874-407F-AE97-6BF8537669BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.05</v>
+        <v>22.24</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22210.579874700001</v>
+        <v>22401.963556160001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.775937618961291E-2</v>
+        <v>5.4592458801828059E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.9081395639608359E-2</v>
+        <v>4.8662085155277181E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.9886621315192746E-2</v>
+        <v>4.9460431654676264E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13460,20 +13460,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.9886621315192746E-2</v>
+        <v>4.9460431654676264E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.9886621315192746E-2</v>
+        <v>4.9460431654676264E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.8956916099773243E-2</v>
+        <v>5.8453237410071947E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.1746031746031744E-2</v>
+        <v>3.1474820143884891E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14659,50 +14659,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9081395639608359E-2</v>
+        <v>4.8662085155277181E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3928472951054754E-2</v>
+        <v>5.3467753083217509E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.446786917877984E-2</v>
+        <v>5.4002541159716533E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.1167782703482897E-2</v>
+        <v>4.081607952391178E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.3656478014989099E-2</v>
+        <v>4.3283513499573281E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4205623684116518E-2</v>
+        <v>3.3913399381059771E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.2217412525464973E-2</v>
+        <v>4.1856742184644906E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.4574091776627791E-2</v>
+        <v>3.427871958968718E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.3564708089822863E-2</v>
+        <v>3.3277959234738953E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.4358346846642497E-2</v>
+        <v>3.4064817804337545E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.1878115654536167E-2</v>
+        <v>3.1605775637703351E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14716,43 +14716,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6888283652570169E-2</v>
+        <v>5.6402277632157022E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6734376324653266E-2</v>
+        <v>5.6249685160009194E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0284720583644166E-2</v>
+        <v>4.9855129895204763E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.61314015563873E-2</v>
+        <v>4.5737293359637589E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7195374936655437E-2</v>
+        <v>3.6877608693941202E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3811669550709711E-2</v>
+        <v>4.3437379208325057E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.491465564495868E-2</v>
+        <v>3.4616373964538621E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8617079859495794E-2</v>
+        <v>2.8372599411055858E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0927372489831413E-2</v>
+        <v>3.0663154829171882E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8286660030684408E-2</v>
+        <v>2.804500241351579E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.05</v>
+        <v>-22.24</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.05</v>
+        <v>22.24</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.05</v>
+        <v>22.24</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.775937618961291E-2</v>
+        <v>5.4592458801828059E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07967095-2874-407F-AE97-6BF8537669BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55D4EB8-EF3E-4284-8B3D-5A53D8F0051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55D4EB8-EF3E-4284-8B3D-5A53D8F0051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1DAAFE-EE91-4DC8-9474-8D7D64E17EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.24</v>
+        <v>22.14</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22401.963556160001</v>
+        <v>22301.235302760004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.4592458801828059E-2</v>
+        <v>5.6254597549256768E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.8662085155277181E-2</v>
+        <v>4.8881877771154665E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.9460431654676264E-2</v>
+        <v>4.9683830171635052E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13460,20 +13460,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.9460431654676264E-2</v>
+        <v>4.9683830171635052E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.9460431654676264E-2</v>
+        <v>4.9683830171635052E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.8453237410071947E-2</v>
+        <v>5.8717253839205057E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.1474820143884891E-2</v>
+        <v>3.1616982836495028E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14659,50 +14659,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8662085155277181E-2</v>
+        <v>4.8881877771154665E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3467753083217509E-2</v>
+        <v>5.3709251516294368E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.4002541159716533E-2</v>
+        <v>5.4246455076427079E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.081607952391178E-2</v>
+        <v>4.1000433993306135E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.3283513499573281E-2</v>
+        <v>4.3479012657204594E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.3913399381059771E-2</v>
+        <v>3.4066576433368079E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.1856742184644906E-2</v>
+        <v>4.2045797027393979E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.427871958968718E-2</v>
+        <v>3.4433546688104916E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.3277959234738953E-2</v>
+        <v>3.3428266187018711E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.4064817804337545E-2</v>
+        <v>3.4218678770030125E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.1605775637703351E-2</v>
+        <v>3.1748529818542114E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14716,43 +14716,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6402277632157022E-2</v>
+        <v>5.665703046699061E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6249685160009194E-2</v>
+        <v>5.6503748778618086E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9855129895204763E-2</v>
+        <v>5.0080311150377317E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5737293359637589E-2</v>
+        <v>4.5943875533800353E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6877608693941202E-2</v>
+        <v>3.7044174225530815E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3437379208325057E-2</v>
+        <v>4.3633573333023902E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4616373964538621E-2</v>
+        <v>3.4772726150466976E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8372599411055858E-2</v>
+        <v>2.8500750266571014E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0663154829171882E-2</v>
+        <v>3.0801651463449983E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.804500241351579E-2</v>
+        <v>2.8171673607795444E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.24</v>
+        <v>-22.14</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.24</v>
+        <v>22.14</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.24</v>
+        <v>22.14</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.4592458801828059E-2</v>
+        <v>5.6254597549256768E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1DAAFE-EE91-4DC8-9474-8D7D64E17EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D005CAC7-AE5A-40CE-88FA-ADB4965D4EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.14</v>
+        <v>21.73</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22301.235302760004</v>
+        <v>21888.249463820001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.6254597549256768E-2</v>
+        <v>6.3178899358375284E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.8881877771154665E-2</v>
+        <v>4.9804177351742494E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.9683830171635052E-2</v>
+        <v>5.0621260929590434E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13460,20 +13460,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.9683830171635052E-2</v>
+        <v>5.0621260929590434E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.9683830171635052E-2</v>
+        <v>5.0621260929590434E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>5.8717253839205057E-2</v>
+        <v>5.9825126553152322E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.1616982836495028E-2</v>
+        <v>3.2213529682466636E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14659,50 +14659,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8881877771154665E-2</v>
+        <v>4.9804177351742494E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>5.3709251516294368E-2</v>
+        <v>5.4722633620375397E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.4246455076427079E-2</v>
+        <v>5.5269973096737021E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.1000433993306135E-2</v>
+        <v>4.1774027087519462E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.3479012657204594E-2</v>
+        <v>4.4299371386585809E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.4066576433368079E-2</v>
+        <v>3.4709342026450492E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.2045797027393979E-2</v>
+        <v>4.2839113952439146E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>3.4433546688104916E-2</v>
+        <v>3.5083236248257842E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>3.3428266187018711E-2</v>
+        <v>3.4058988190547361E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>3.4218678770030125E-2</v>
+        <v>3.4864314218521264E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.1748529818542114E-2</v>
+        <v>3.2347558683042912E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14716,43 +14716,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.665703046699061E-2</v>
+        <v>5.7726031041839494E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6503748778618086E-2</v>
+        <v>5.7569857246139187E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0080311150377317E-2</v>
+        <v>5.1025222681516519E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5943875533800353E-2</v>
+        <v>4.6810741109909799E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7044174225530815E-2</v>
+        <v>3.7743120909031404E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3633573333023902E-2</v>
+        <v>4.4456848301571525E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4772726150466976E-2</v>
+        <v>3.5428815323117299E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8500750266571014E-2</v>
+        <v>2.9038500271600657E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0801651463449983E-2</v>
+        <v>3.1382814698609415E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8171673607795444E-2</v>
+        <v>2.8703214619263288E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.14</v>
+        <v>-21.73</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.14</v>
+        <v>21.73</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.14</v>
+        <v>21.73</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.6254597549256768E-2</v>
+        <v>6.3178899358375284E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D005CAC7-AE5A-40CE-88FA-ADB4965D4EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26100D7-11D6-4CB7-B114-6E97D458E395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2445,6 +2434,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
@@ -2470,9 +2471,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3149,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3894,6 +3892,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4223,10 +4225,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4238,18 +4240,18 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4263,7 +4265,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4272,10 +4274,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4289,7 +4291,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4299,7 +4301,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4312,20 +4314,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4341,17 +4343,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4365,7 +4367,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4391,35 +4393,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4427,7 +4429,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4437,26 +4439,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4477,11 +4479,11 @@
         <v>22.601441956902718</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.3178899358375284E-2</v>
+        <v>5.8178449457329418E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4490,7 +4492,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4501,7 +4503,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4509,37 +4511,37 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>11.355103666814504</v>
+        <v>11.165268338950117</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>15.879140273250821</v>
+        <v>15.642626483276317</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F30" s="312">
         <v>0.187</v>
@@ -4547,18 +4549,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>21.916919635758642</v>
+        <v>21.622888321317863</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F31" s="312">
         <v>0.06</v>
@@ -4566,18 +4568,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>20.396738931178472</v>
+        <v>20.116801024749044</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4589,7 +4591,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4597,45 +4599,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4650,18 +4652,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4674,7 +4676,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4686,17 +4688,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4708,17 +4710,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4733,7 +4735,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4748,7 +4750,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4761,12 +4763,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4778,17 +4780,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4800,17 +4802,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4821,27 +4823,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4854,7 +4856,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4867,24 +4869,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>4.9804177351742494E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
-        <v>5.0621260929590434E-2</v>
+        <f>Normalized_FCF!C94</f>
+        <v>4.555913483663139E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4893,73 +4895,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>450</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>0.15161114820375229</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>0.16779050789746269</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>0.3932476207375345</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>0.41423799416800827</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.30212796693987309</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.31742662653511533</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.2760688428830085</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.2760688428830085</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4970,33 +4972,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5005,7 +5007,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5014,7 +5016,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5026,31 +5028,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5058,7 +5060,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5071,7 +5073,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5083,36 +5085,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5125,7 +5127,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5138,7 +5140,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5147,7 +5149,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5156,12 +5158,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5174,7 +5176,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5187,7 +5189,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5200,12 +5202,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5218,7 +5220,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5229,18 +5231,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+    <row r="116" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5253,7 +5255,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5266,7 +5268,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5274,30 +5276,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+    <row r="123" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5412,7 +5414,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5423,18 +5425,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+    <row r="134" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5443,31 +5445,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5476,20 +5478,20 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.1000000000000001</v>
+        <v>0.9900000000000001</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5498,7 +5500,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5511,11 +5513,11 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5525,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8983532786438633</v>
+        <v>1.7085179507794768</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5540,11 +5542,11 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>11.355103666814504</v>
+        <v>11.165268338950117</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5553,7 +5555,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5566,21 +5568,21 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.4975938398768166</v>
+        <v>0.50599309724395147</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5594,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.365137899745049</v>
+        <v>2.1286241097705441</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5609,11 +5611,11 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>15.879140273250821</v>
+        <v>15.642626483276317</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5622,7 +5624,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5635,21 +5637,21 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.29742800023424332</v>
+        <v>0.30789254450648473</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5663,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>2.9403131444078037</v>
+        <v>2.6462818299670237</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5678,11 +5680,11 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>21.916919635758642</v>
+        <v>21.622888321317863</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5691,7 +5693,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5704,21 +5706,21 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>3.0286665888368924E-2</v>
+        <v>4.3296070996301839E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5732,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>2.7993790642942851</v>
+        <v>2.5194411578648568</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5747,11 +5749,11 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>20.396738931178472</v>
+        <v>20.116801024749044</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5760,7 +5762,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5773,16 +5775,16 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.11969174215505141</v>
+        <v>0.13177365640345884</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5791,98 +5793,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+    </row>
+    <row r="191" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5920,7 +5922,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -5944,12 +5946,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -6187,7 +6189,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6203,7 +6205,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6219,7 +6221,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6471,7 +6473,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>1796295378</v>
@@ -6507,7 +6509,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-63639368</v>
@@ -6543,7 +6545,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-1858931831</v>
@@ -6608,7 +6610,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6761,7 +6763,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7162,7 +7164,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7211,7 +7213,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7559,12 +7561,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7613,7 +7615,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7662,7 +7664,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7711,7 +7713,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7913,7 +7915,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8165,7 +8167,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8531,15 +8533,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8560,7 +8562,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8571,19 +8573,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8644,7 +8646,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8665,7 +8667,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8676,7 +8678,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8686,7 +8688,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8707,7 +8709,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8771,19 +8773,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8791,7 +8793,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8820,7 +8822,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8840,7 +8842,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8851,7 +8853,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>1386748288</v>
@@ -8860,7 +8862,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8881,7 +8883,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>28358189</v>
@@ -8901,7 +8903,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8921,7 +8923,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>5983606533</v>
@@ -8981,16 +8983,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -9023,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>4958355</v>
@@ -9067,7 +9069,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9117,10 +9119,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9128,10 +9130,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9153,7 +9155,7 @@
         <v>1085000000</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9169,7 +9171,7 @@
         <v>35712104</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9185,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9214,14 +9216,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>1120712104</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9241,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9260,7 +9262,7 @@
         <v>1120712104</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9284,13 +9286,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9298,7 +9300,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9330,7 +9332,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9357,7 +9359,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9371,7 +9373,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9383,7 +9385,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9397,7 +9399,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9414,7 +9416,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9451,10 +9453,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9463,7 +9465,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9474,12 +9476,12 @@
         <v>5.1365522139309278E-4</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9490,13 +9492,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9504,7 +9506,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9515,12 +9517,12 @@
         <v>3438409570.5196743</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9530,7 +9532,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9540,7 +9542,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9550,7 +9552,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9563,7 +9565,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9575,7 +9577,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9586,12 +9588,12 @@
         <v>-273848514.74016273</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9602,12 +9604,12 @@
         <v>14.555881757409422</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9615,12 +9617,12 @@
         <v>547697029.48032546</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9628,7 +9630,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9636,10 +9638,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9648,7 +9650,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9662,7 +9664,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9676,7 +9678,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9690,7 +9692,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9704,7 +9706,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9715,15 +9717,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>289</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9740,7 +9742,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9757,7 +9759,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9774,7 +9776,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9802,17 +9804,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Q809"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10134,7 +10136,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10301,7 +10303,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10413,7 +10415,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10523,7 +10525,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10580,7 +10582,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10645,7 +10647,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10670,7 +10672,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10764,7 +10766,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -10983,7 +10985,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -10998,7 +11000,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11058,7 +11060,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11175,14 +11177,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-121114559.75</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11240,7 +11242,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11352,7 +11354,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11534,21 +11536,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11602,7 +11604,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11687,7 +11689,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11742,7 +11744,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11858,11 +11860,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11874,7 +11876,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11901,7 +11903,7 @@
         <v>4.3098432538541648E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11980,17 +11982,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12045,7 +12047,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12100,7 +12102,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12155,7 +12157,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12210,13 +12212,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12266,7 +12268,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12325,17 +12327,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12360,7 +12362,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12385,7 +12387,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12410,7 +12412,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12440,12 +12442,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>464</v>
+        <v>59</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12463,7 +12465,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12655,7 +12657,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12828,7 +12830,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12942,7 +12944,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13114,7 +13116,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13221,7 +13223,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13282,7 +13284,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13401,7 +13403,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13456,1310 +13458,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
-        <v>5.0621260929590434E-2</v>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0.1</v>
       </c>
       <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>5.0621260929590434E-2</v>
-      </c>
-      <c r="H93" s="23">
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
+        <v>4.555913483663139E-2</v>
+      </c>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>4.555913483663139E-2</v>
+      </c>
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.9825126553152322E-2</v>
-      </c>
-      <c r="I93" s="23">
+        <v>5.3842613897837101E-2</v>
+      </c>
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.2213529682466636E-2</v>
-      </c>
-      <c r="J93" s="23">
+        <v>2.8992176714219973E-2</v>
+      </c>
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>-4.8195892582280853E-2</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-1.054538142135597E-2</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.14858922330117963</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>-4.007443085169593E-2</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.15760498338398921</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.12248447173608201</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.11334182197031795</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.14614594368347511</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.17751920290006873</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>3.4394484333802877E-2</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-9.6425953389435159E-2</v>
+        <f>C4/G4-1</f>
+        <v>-4.8195892582280853E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>-1.054538142135597E-2</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.14858922330117963</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>-4.007443085169593E-2</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.15760498338398921</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.12248447173608201</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.11334182197031795</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.14614594368347511</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.17751920290006873</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>3.4394484333802877E-2</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-9.6425953389435159E-2</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>-6.3117174890822136E-3</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>0.26201456633021136</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>-1.5324914837187786E-2</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>0.26262486459047274</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>-0.17940837548336741</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>0.23085154520059925</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>7.2287842445268202E-2</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>-3.5842178608927799E-2</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>8.2670067434333916E-2</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>12324321966</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>12324321966</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>12881135035</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>12827290298</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>12725924787</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>12090123296</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>11802423892</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>11092727799</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>11666019297</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>11208470938</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>10219156999</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>228574200</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>258206405</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>377357021</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>368491616</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>440548083</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>421649740</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>30681363</v>
+        <f>BS!C4</f>
+        <v>228574200</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>258206405</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>377357021</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>368491616</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>440548083</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>421649740</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="346">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="346">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>30681363</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>32289866</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>32129347</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>32745245</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>33982961</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>32833169</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346">
+      <c r="N104" s="346">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="346">
+      <c r="O104" s="346">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="346">
+      <c r="P104" s="346">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>2666283503</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>2666283503</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>3177151047</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>3678311933</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>4088929705</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>4074330379</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>4229364458</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>4170411465</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>5196347300</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>5071716119</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>4567360550</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>9658038463</v>
+        <f>BS!G30</f>
+        <v>2666283503</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>2666283503</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>3177151047</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>3678311933</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>4088929705</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>4074330379</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>4229364458</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>4170411465</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>5196347300</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>5071716119</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>4567360550</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>9658038463</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>9658038463</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>9703983988</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>9148978365</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>8636995082</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>8015792917</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>7573059434</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>6922316334</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>6469671997</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>6136754819</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>5651796449</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>6.1386552613161782E-2</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>6.6002535887448005E-2</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>9.5442526161463648E-2</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.10704880885840756</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.12285281263728376</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.13611438103978038</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>8.2398761716896106E-3</v>
+        <v>6.1386552613161782E-2</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>8.2539123669913891E-3</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>6.6002535887448005E-2</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>8.1262726567852654E-3</v>
+        <f t="shared" si="43"/>
+        <v>9.5442526161463648E-2</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>9.512670901654181E-3</v>
+        <f t="shared" si="43"/>
+        <v>0.10704880885840756</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>9.4766099358855257E-3</v>
+        <f t="shared" si="43"/>
+        <v>0.12285281263728376</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>1.059900209118949E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.13611438103978038</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
+        <f>C104/C$4</f>
+        <v>8.2398761716896106E-3</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>8.2539123669913891E-3</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>8.1262726567852654E-3</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>9.512670901654181E-3</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>9.4766099358855257E-3</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>1.059900209118949E-2</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>1.4216576425456566</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>1.5226218146604997</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>1.6334571862107776</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>1.7374243098570166</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>1.7025420861721461</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>1.5796932173236939</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>1.8627422049853775</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>1.896621583302976</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>1.6233370543232535</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>1.8217798115484487</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>1.4216576425456566</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>1.5226218146604997</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>1.6334571862107776</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>1.7374243098570166</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>1.7025420861721461</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>1.5796932173236939</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>1.8627422049853775</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>1.896621583302976</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>1.6233370543232535</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>1.8217798115484487</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.4996839109348399</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.5859808789202645</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.995199469098575</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.8359203984417687</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>1.8513532109637996</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.6393472050694062</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.8810907040618412</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.6170488111315213</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.4612329859667579</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>1.6165342625169379</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>0.3932476207375345</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.41423799416800827</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.41247311026411931</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.37540150644103165</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.36596590099561049</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.33552638049666283</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.3588016258409199</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.32454673952945173</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>0.34690119044818407</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>0.42366799729143706</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>0.40477690551243689</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.30212796693987309</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.31742662653511533</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.30694204060876845</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.26835571488833548</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.28178564159543151</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.25622239973556676</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.29910371372043582</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.28584206089379044</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>0.23713839618895668</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>0.20960913241384718</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>0.22225692581318174</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.2760688428830085</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.2760688428830085</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.3274068723659151</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>1.4020461942583247</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>1.47342040445543</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>1.5082878788396723</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>1.5584750119630448</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.6024589550345159</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>1.8031855869060374</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>1.8264492013429419</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>1.8081254502377073</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>0.15161114820375229</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>0.16779050789746269</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>0.16805679595274287</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>0.14124373142508792</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>0.15194491180561262</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>0.12966656533699472</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>0.16725382205682554</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>0.14865868928087042</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>0.14833652331138419</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>0.16219723931584368</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>0.16266704901636489</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (CNY)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0822447738533645</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.1891228285707574</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.2010165153920955</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.90774960861179788</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.96262534023050972</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.75423400223476922</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.93089394618650267</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.76235872367464286</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.74010181338059422</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.75760154796846702</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.70291245018252246</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9804177351742494E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (CNY)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>1.0822447738533645</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>1.1891228285707574</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.2010165153920955</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.90774960861179788</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.96262534023050972</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.75423400223476922</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.93089394618650267</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.76235872367464286</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.74010181338059422</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.75760154796846702</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.70291245018252246</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>4.9804177351742494E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>5.4722633620375397E-2</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>5.5269973096737021E-2</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>4.1774027087519462E-2</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>4.4299371386585809E-2</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>3.4709342026450492E-2</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>4.2839113952439146E-2</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>3.5083236248257842E-2</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>3.4058988190547361E-2</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>3.4864314218521264E-2</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>3.2347558683042912E-2</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.7726031041839494E-2</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.7569857246139187E-2</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.1025222681516519E-2</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>4.6810741109909799E-2</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>3.7743120909031404E-2</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>4.4456848301571525E-2</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>3.5428815323117299E-2</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.9038500271600657E-2</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>3.1382814698609415E-2</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.8703214619263288E-2</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15441,6 +15463,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15462,13 +15485,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15485,20 +15508,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15509,7 +15532,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15519,7 +15542,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15528,9 +15551,9 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15540,15 +15563,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15558,13 +15581,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15574,13 +15597,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15590,13 +15613,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15610,7 +15633,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15641,7 +15664,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15651,13 +15674,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15665,9 +15688,9 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15675,7 +15698,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15700,7 +15723,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -16472,7 +16495,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16509,7 +16532,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16730,7 +16753,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16959,19 +16982,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17096,7 +17119,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17222,18 +17245,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17245,31 +17268,31 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
-        <v>1108010787.4000001</v>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
+        <v>997209708.66000009</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17279,7 +17302,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17288,29 +17311,29 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>18466846456.666668</v>
+        <v>16620161811.000002</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>18.333333333333336</v>
+        <v>16.500000000000004</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17323,7 +17346,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17333,13 +17356,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1">
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17347,9 +17370,9 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1">
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17357,13 +17380,13 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1">
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.717224260427621</v>
+        <v>18.645501834384856</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17379,16 +17402,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17398,7 +17421,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>1155027008.0543618</v>
+        <v>1039524307.2489256</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17410,7 +17433,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>1089648120.8060017</v>
+        <v>980683308.7254014</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17420,7 +17443,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>1204038267.9536092</v>
+        <v>1083634441.1582482</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17432,7 +17455,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>1071589772.1196235</v>
+        <v>964430794.90766108</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17442,7 +17465,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>1255129222.5960624</v>
+        <v>1129616300.3364561</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17454,7 +17477,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>1053830697.988996</v>
+        <v>948447628.19009626</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17464,7 +17487,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>1308388119.6667192</v>
+        <v>1177549307.7000473</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17476,7 +17499,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>1036365938.6439171</v>
+        <v>932729344.77952528</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17486,7 +17509,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>1363906951.4645078</v>
+        <v>1227516256.3180571</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17498,7 +17521,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>1019190616.5106819</v>
+        <v>917271554.85961366</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17508,7 +17531,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>1421781613.7974868</v>
+        <v>1279603452.4177382</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -17520,7 +17543,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>1002299934.8498714</v>
+        <v>902069941.36488426</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -17530,7 +17553,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>1482112071.6204438</v>
+        <v>1333900864.4583995</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -17542,7 +17565,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>985689176.41671324</v>
+        <v>887120258.77504206</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -17552,7 +17575,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>1545002531.7009954</v>
+        <v>1390502278.5308957</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -17564,7 +17587,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>969353702.14364696</v>
+        <v>872418331.92928219</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -17574,7 +17597,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>1610561622.6124251</v>
+        <v>1449505460.3511825</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -17586,7 +17609,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>953288949.84471834</v>
+        <v>857960054.86024642</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -17596,7 +17619,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>1678902582.364161</v>
+        <v>1511012324.1277447</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -17608,7 +17631,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>937490432.94145095</v>
+        <v>843741389.64730573</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18054,11 +18077,11 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>19250450134.239365</v>
+        <v>17325405120.815426</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18070,7 +18093,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>10749350808.22419</v>
+        <v>9674415727.4017696</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18081,7 +18104,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>20868098150.489811</v>
+        <v>18781288335.440826</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18091,7 +18114,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18102,7 +18125,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>20868098150.489811</v>
+        <v>18781288335.440826</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18132,19 +18155,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>18466846456.666664</v>
+        <v>16620161810.999996</v>
       </c>
       <c r="C51" s="123">
-        <v>18741175611.322224</v>
+        <v>16867058050.189999</v>
       </c>
       <c r="D51" s="123">
-        <v>19300536731.652786</v>
+        <v>17370483058.487511</v>
       </c>
       <c r="E51" s="123">
-        <v>19874695345.828362</v>
+        <v>17887225811.245522</v>
       </c>
       <c r="F51" s="123">
-        <v>20167525995.315155</v>
+        <v>18150773395.783642</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18153,19 +18176,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>18466846456.66666</v>
+        <v>16620161810.999994</v>
       </c>
       <c r="C52" s="123">
-        <v>18991280365.18211</v>
+        <v>17092152328.663898</v>
       </c>
       <c r="D52" s="123">
-        <v>20114988373.02565</v>
+        <v>18103489535.723083</v>
       </c>
       <c r="E52" s="123">
-        <v>21348544842.942421</v>
+        <v>19213690358.648178</v>
       </c>
       <c r="F52" s="123">
-        <v>22010605917.945885</v>
+        <v>19809545326.151299</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18174,19 +18197,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>18466846456.666656</v>
+        <v>16620161810.999989</v>
       </c>
       <c r="C53" s="123">
-        <v>19321979486.83147</v>
+        <v>17389781538.148323</v>
       </c>
       <c r="D53" s="123">
-        <v>21248085626.597767</v>
+        <v>19123277063.937992</v>
       </c>
       <c r="E53" s="123">
-        <v>23510225834.047466</v>
+        <v>21159203250.642715</v>
       </c>
       <c r="F53" s="123">
-        <v>24788065807.835007</v>
+        <v>22309259227.05151</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18195,19 +18218,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>18466846456.666656</v>
+        <v>16620161810.999989</v>
       </c>
       <c r="C54" s="123">
-        <v>19682039103.498722</v>
+        <v>17713835193.148849</v>
       </c>
       <c r="D54" s="123">
-        <v>22549156840.774757</v>
+        <v>20294241156.697281</v>
       </c>
       <c r="E54" s="123">
-        <v>26136813566.439171</v>
+        <v>23523132209.79525</v>
       </c>
       <c r="F54" s="123">
-        <v>28263748764.820301</v>
+        <v>25437373888.338268</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18216,19 +18239,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>18466846456.666656</v>
+        <v>16620161810.999985</v>
       </c>
       <c r="C55" s="123">
-        <v>20039798510.26284</v>
+        <v>18035818659.236553</v>
       </c>
       <c r="D55" s="123">
-        <v>23914990264.151142</v>
+        <v>21523491237.736034</v>
       </c>
       <c r="E55" s="123">
-        <v>29063997564.813316</v>
+        <v>26157597808.331974</v>
       </c>
       <c r="F55" s="123">
-        <v>32261184615.1768</v>
+        <v>29035066153.659107</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18237,19 +18260,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>18466846456.666656</v>
+        <v>16620161810.999983</v>
       </c>
       <c r="C56" s="123">
-        <v>20376801493.135548</v>
+        <v>18339121343.821991</v>
       </c>
       <c r="D56" s="123">
-        <v>25276584773.014618</v>
+        <v>22748926295.713158</v>
       </c>
       <c r="E56" s="123">
-        <v>32171162191.079746</v>
+        <v>28954045971.971764</v>
       </c>
       <c r="F56" s="123">
-        <v>36648504579.321442</v>
+        <v>32983654121.389282</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18262,7 +18285,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18299,23 +18322,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>18.333333333333336</v>
+        <v>16.500000000000004</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>18.333333333333336</v>
+        <v>16.500000000000004</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>18.333333333333336</v>
+        <v>16.500000000000004</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>18.333333333333336</v>
+        <v>16.500000000000004</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>18.333333333333336</v>
+        <v>16.500000000000004</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18326,23 +18349,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>18.333333333333332</v>
+        <v>16.499999999999996</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>18.605679120533846</v>
+        <v>16.745111208480459</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>19.160996125892108</v>
+        <v>17.244896513302901</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>19.731003640958953</v>
+        <v>17.757903276863054</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>20.021717159363707</v>
+        <v>18.019545443427337</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18353,23 +18376,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>18.333333333333329</v>
+        <v>16.499999999999993</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>18.853975646501294</v>
+        <v>16.968578081851163</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>19.969559377891137</v>
+        <v>17.972603440102024</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>21.194197379920439</v>
+        <v>19.074777641928396</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>21.85147183138379</v>
+        <v>19.666324648245414</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18380,23 +18403,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>18.333333333333321</v>
+        <v>16.499999999999989</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>19.182283852478147</v>
+        <v>17.264055467230332</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>21.094464471869586</v>
+        <v>18.985018024682628</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>23.340249672240883</v>
+        <v>21.006224705016791</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>24.60885101362733</v>
+        <v>22.147965912264603</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18407,23 +18430,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>18.333333333333321</v>
+        <v>16.499999999999989</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>19.539740280554415</v>
+        <v>17.585766252498974</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>22.38612909451556</v>
+        <v>20.147516185064003</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>25.947847484903548</v>
+        <v>23.35306273641319</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>28.059405192486242</v>
+        <v>25.253464673237616</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18434,23 +18457,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>18.333333333333321</v>
+        <v>16.499999999999986</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>19.894913128974039</v>
+        <v>17.905421816076633</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>23.742087703221451</v>
+        <v>21.367878932899313</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>28.85386828797462</v>
+        <v>25.968481459177148</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>32.027940052792374</v>
+        <v>28.825146047513126</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18460,40 +18483,40 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>18.333333333333321</v>
+        <v>16.499999999999982</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>20.229479620000586</v>
+        <v>18.206531658000525</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>25.09383804426675</v>
+        <v>22.584454239840078</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>31.938568480211281</v>
+        <v>28.744711632190143</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>36.383540210696673</v>
+        <v>32.745186189626992</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18511,7 +18534,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>24.60885101362733</v>
+        <v>22.147965912264603</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18533,7 +18556,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>21.194197379920439</v>
+        <v>19.074777641928396</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18556,7 +18579,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>19.969559377891137</v>
+        <v>17.972603440102024</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18579,7 +18602,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>18.853975646501294</v>
+        <v>16.968578081851163</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18602,7 +18625,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>18.333333333333321</v>
+        <v>16.499999999999989</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18618,7 +18641,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18670,32 +18693,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="6" width="42.6640625" customWidth="1"/>
-    <col min="8" max="9" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="6" width="42.73046875" customWidth="1"/>
+    <col min="8" max="9" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18707,14 +18730,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18722,7 +18745,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.1000000000000001</v>
+        <v>0.9900000000000001</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18731,7 +18754,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>0.9900000000000001</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18743,7 +18766,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18751,12 +18774,12 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>23.70144195690272</v>
+        <v>23.591441956902717</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18766,11 +18789,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国国贸(600007.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18791,8 +18814,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18813,8 +18836,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18824,8 +18847,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18836,10 +18859,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>447</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>444</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18850,15 +18873,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>2.9436096404119594E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18869,14 +18892,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.4272741432500604E-2</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18893,12 +18916,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>7.2975508413014145E-2</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18907,38 +18930,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18948,12 +18971,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18963,44 +18986,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19010,55 +19033,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19068,55 +19091,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19126,24 +19149,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19156,7 +19179,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19165,12 +19188,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>15</v>
@@ -19185,39 +19208,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19227,55 +19250,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19285,23 +19308,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19312,7 +19335,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19321,7 +19344,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19330,15 +19353,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19346,19 +19369,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
         <v>4.2432999018617502E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19374,20 +19397,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19397,19 +19420,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19419,14 +19442,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19435,7 +19458,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19444,12 +19467,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19459,11 +19482,11 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
-        <v>1.1000000000000001</v>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
+        <v>0.9900000000000001</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19472,25 +19495,25 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8983532786438633</v>
+        <v>1.7085179507794768</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19498,7 +19521,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19512,18 +19535,18 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>11.355103666814504</v>
+        <v>11.165268338950117</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.4975938398768166</v>
+        <v>0.50599309724395147</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19531,12 +19554,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19549,11 +19572,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.3178899358375284E-2</v>
+        <v>5.8178449457329418E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19561,12 +19584,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19575,11 +19598,11 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.365137899745049</v>
+        <v>2.1286241097705441</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19587,7 +19610,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19601,30 +19624,30 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>15.879140273250821</v>
+        <v>15.642626483276317</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.29742800023424332</v>
+        <v>0.30789254450648473</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19635,11 +19658,11 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.9403131444078037</v>
+        <v>2.6462818299670237</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19647,7 +19670,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19659,21 +19682,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>21.916919635758642</v>
+        <v>21.622888321317863</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>3.0286665888368924E-2</v>
+        <v>4.3296070996301839E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19681,12 +19704,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19695,17 +19718,17 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.7993790642942851</v>
+        <v>2.5194411578648568</v>
       </c>
       <c r="D103" s="116"/>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19715,21 +19738,21 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>20.396738931178472</v>
+        <v>20.116801024749044</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.11969174215505141</v>
+        <v>0.13177365640345884</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19737,32 +19760,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
+        <v>322</v>
+      </c>
+      <c r="F110" s="284" t="s">
         <v>325</v>
-      </c>
-      <c r="F110" s="284" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26100D7-11D6-4CB7-B114-6E97D458E395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD74DC89-FC29-4D2F-A299-571EA47D0247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.73</v>
+        <v>22.1</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21888.249463820001</v>
+        <v>22260.944001400003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.8178449457329418E-2</v>
+        <v>5.1979747974227886E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.9804177351742494E-2</v>
+        <v>4.8970351758070782E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.555913483663139E-2</v>
+        <v>4.4796380090497738E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.7085179507794768</v>
+        <v>1.7085179507794772</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.555913483663139E-2</v>
+        <v>4.4796380090497738E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.555913483663139E-2</v>
+        <v>4.4796380090497738E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.3842613897837101E-2</v>
+        <v>5.2941176470588241E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.8992176714219973E-2</v>
+        <v>2.8506787330316741E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9804177351742494E-2</v>
+        <v>4.8970351758070782E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.4722633620375397E-2</v>
+        <v>5.3806462831255987E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5269973096737021E-2</v>
+        <v>5.4344638705524681E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.1774027087519462E-2</v>
+        <v>4.1074642923610759E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.4299371386585809E-2</v>
+        <v>4.3557707702737994E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.4709342026450492E-2</v>
+        <v>3.4128235395238425E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.2839113952439146E-2</v>
+        <v>4.2121898017488807E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.5083236248257842E-2</v>
+        <v>3.4495869849531346E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.4058988190547361E-2</v>
+        <v>3.3488769836225979E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.4864314218521264E-2</v>
+        <v>3.4280613030247375E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.2347558683042912E-2</v>
+        <v>3.1805993220928613E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7726031041839494E-2</v>
+        <v>5.6759577128469331E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7569857246139187E-2</v>
+        <v>5.660601800717667E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1025222681516519E-2</v>
+        <v>5.0170954247482073E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6810741109909799E-2</v>
+        <v>4.6027031869608138E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7743120909031404E-2</v>
+        <v>3.7111222504672046E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4456848301571525E-2</v>
+        <v>4.3712548126386842E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5428815323117299E-2</v>
+        <v>3.4835663211372797E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9038500271600657E-2</v>
+        <v>2.8552335334926796E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1382814698609415E-2</v>
+        <v>3.0857401058858942E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8703214619263288E-2</v>
+        <v>2.8222663062289193E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.73</v>
+        <v>-22.1</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.73</v>
+        <v>22.1</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.7085179507794768</v>
+        <v>1.7085179507794772</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.73</v>
+        <v>22.1</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.8178449457329418E-2</v>
+        <v>5.1979747974227886E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD74DC89-FC29-4D2F-A299-571EA47D0247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A7F4EF-5CAA-48DE-A1F6-76CBE2589005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.1</v>
+        <v>21.78</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22260.944001400003</v>
+        <v>21938.613590519999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.1979747974227886E-2</v>
+        <v>5.7332356754072666E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.8970351758070782E-2</v>
+        <v>4.968984269299194E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4796380090497738E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4796380090497738E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4796380090497738E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.2941176470588241E-2</v>
+        <v>5.3719008264462811E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.8506787330316741E-2</v>
+        <v>2.8925619834710741E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8970351758070782E-2</v>
+        <v>4.968984269299194E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.3806462831255987E-2</v>
+        <v>5.459700773970419E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.4344638705524681E-2</v>
+        <v>5.5143090697525043E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.1074642923610759E-2</v>
+        <v>4.1678127117162435E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.3557707702737994E-2</v>
+        <v>4.4197674023439382E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.4128235395238425E-2</v>
+        <v>3.4629660341357629E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.2121898017488807E-2</v>
+        <v>4.2740768879086441E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.4495869849531346E-2</v>
+        <v>3.5002696220139705E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.3488769836225979E-2</v>
+        <v>3.3980799512423977E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.4280613030247375E-2</v>
+        <v>3.4784276766228972E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.1805993220928613E-2</v>
+        <v>3.2273298906451905E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6759577128469331E-2</v>
+        <v>5.7593510309420212E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.660601800717667E-2</v>
+        <v>5.7437695039421692E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0170954247482073E-2</v>
+        <v>5.0908084888400089E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6027031869608138E-2</v>
+        <v>4.6703278435185486E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7111222504672046E-2</v>
+        <v>3.7656474625952813E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3712548126386842E-2</v>
+        <v>4.435478942117306E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4835663211372797E-2</v>
+        <v>3.5347481954606928E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8552335334926796E-2</v>
+        <v>2.8971837047836652E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0857401058858942E-2</v>
+        <v>3.1310769669457422E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8222663062289193E-2</v>
+        <v>2.8637321105444959E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.1</v>
+        <v>-21.78</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.1</v>
+        <v>21.78</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.1</v>
+        <v>21.78</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.1979747974227886E-2</v>
+        <v>5.7332356754072666E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A7F4EF-5CAA-48DE-A1F6-76CBE2589005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7A7B81-FE14-458A-875A-73EBADE8CB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21938.613590519999</v>
+        <v>21978.90489188</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.7332356754072666E-2</v>
+        <v>5.6657398786469804E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.968984269299194E-2</v>
+        <v>4.9598752238925958E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.5371219065077913E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.5371219065077913E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.5371219065077913E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.3719008264462811E-2</v>
+        <v>5.3620531622364812E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.8925619834710741E-2</v>
+        <v>2.8872593950504125E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.968984269299194E-2</v>
+        <v>4.9598752238925958E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.459700773970419E-2</v>
+        <v>5.4496921566029206E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5143090697525043E-2</v>
+        <v>5.5042003455183112E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.1678127117162435E-2</v>
+        <v>4.1601723584408702E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.4197674023439382E-2</v>
+        <v>4.4116651706256171E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.4629660341357629E-2</v>
+        <v>3.4566177920933513E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.2740768879086441E-2</v>
+        <v>4.26624173321037E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.5002696220139705E-2</v>
+        <v>3.4938529957591329E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.3980799512423977E-2</v>
+        <v>3.3918506571062983E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.4784276766228972E-2</v>
+        <v>3.4720510905979239E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.2273298906451905E-2</v>
+        <v>3.2214136122022112E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7593510309420212E-2</v>
+        <v>5.7487931005461602E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7437695039421692E-2</v>
+        <v>5.7332401372988291E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0908084888400089E-2</v>
+        <v>5.0814761176414015E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6703278435185486E-2</v>
+        <v>4.6617662892682855E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7656474625952813E-2</v>
+        <v>3.7587443508398363E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.435478942117306E-2</v>
+        <v>4.4273479083095743E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5347481954606928E-2</v>
+        <v>3.5282683637549904E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8971837047836652E-2</v>
+        <v>2.891872643913301E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1310769669457422E-2</v>
+        <v>3.125337137492129E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8637321105444959E-2</v>
+        <v>2.858482372486669E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.78</v>
+        <v>-21.82</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.7332356754072666E-2</v>
+        <v>5.6657398786469804E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7A7B81-FE14-458A-875A-73EBADE8CB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32500C77-C22A-48B3-892E-1685F20F7520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.82</v>
+        <v>21.78</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21978.90489188</v>
+        <v>21938.613590519999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.6657398786469804E-2</v>
+        <v>5.7332356754072666E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.9598752238925958E-2</v>
+        <v>4.968984269299194E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5371219065077913E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5371219065077913E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5371219065077913E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.3620531622364812E-2</v>
+        <v>5.3719008264462811E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.8872593950504125E-2</v>
+        <v>2.8925619834710741E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9598752238925958E-2</v>
+        <v>4.968984269299194E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.4496921566029206E-2</v>
+        <v>5.459700773970419E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5042003455183112E-2</v>
+        <v>5.5143090697525043E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.1601723584408702E-2</v>
+        <v>4.1678127117162435E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.4116651706256171E-2</v>
+        <v>4.4197674023439382E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.4566177920933513E-2</v>
+        <v>3.4629660341357629E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.26624173321037E-2</v>
+        <v>4.2740768879086441E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.4938529957591329E-2</v>
+        <v>3.5002696220139705E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.3918506571062983E-2</v>
+        <v>3.3980799512423977E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.4720510905979239E-2</v>
+        <v>3.4784276766228972E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.2214136122022112E-2</v>
+        <v>3.2273298906451905E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7487931005461602E-2</v>
+        <v>5.7593510309420212E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7332401372988291E-2</v>
+        <v>5.7437695039421692E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0814761176414015E-2</v>
+        <v>5.0908084888400089E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6617662892682855E-2</v>
+        <v>4.6703278435185486E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7587443508398363E-2</v>
+        <v>3.7656474625952813E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4273479083095743E-2</v>
+        <v>4.435478942117306E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5282683637549904E-2</v>
+        <v>3.5347481954606928E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.891872643913301E-2</v>
+        <v>2.8971837047836652E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.125337137492129E-2</v>
+        <v>3.1310769669457422E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.858482372486669E-2</v>
+        <v>2.8637321105444959E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.82</v>
+        <v>-21.78</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.82</v>
+        <v>21.78</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.82</v>
+        <v>21.78</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.6657398786469804E-2</v>
+        <v>5.7332356754072666E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32500C77-C22A-48B3-892E-1685F20F7520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED6BEDD-FBF0-425F-9F22-E7CBF37046E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.78</v>
+        <v>21.55</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21938.613590519999</v>
+        <v>21706.938607700002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.7332356754072666E-2</v>
+        <v>6.1246638871899295E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.968984269299194E-2</v>
+        <v>5.0220175120805774E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.5939675174013928E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.5939675174013928E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.5939675174013928E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.3719008264462811E-2</v>
+        <v>5.4292343387471E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.8925619834710741E-2</v>
+        <v>2.9234338747099766E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.968984269299194E-2</v>
+        <v>5.0220175120805774E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.459700773970419E-2</v>
+        <v>5.5179713622772963E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5143090697525043E-2</v>
+        <v>5.5731624844180767E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.1678127117162435E-2</v>
+        <v>4.2122951675721478E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.4197674023439382E-2</v>
+        <v>4.4669389337842674E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.4629660341357629E-2</v>
+        <v>3.4999257644304838E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.2740768879086441E-2</v>
+        <v>4.3196934857842352E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.5002696220139705E-2</v>
+        <v>3.5376274880493865E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.3980799512423977E-2</v>
+        <v>3.4343471618589055E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.4784276766228972E-2</v>
+        <v>3.5155524267678283E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.2273298906451905E-2</v>
+        <v>3.2617747108237699E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7593510309420212E-2</v>
+        <v>5.8208197426411701E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7437695039421692E-2</v>
+        <v>5.8050719162812271E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0908084888400089E-2</v>
+        <v>5.1451419437092985E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6703278435185486E-2</v>
+        <v>4.7201735699226907E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7656474625952813E-2</v>
+        <v>3.8058376675324933E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.435478942117306E-2</v>
+        <v>4.4828181605250546E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5347481954606928E-2</v>
+        <v>3.5724740462707141E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8971837047836652E-2</v>
+        <v>2.9281049229785718E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1310769669457422E-2</v>
+        <v>3.1644944937391305E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8637321105444959E-2</v>
+        <v>2.8942963047637642E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.78</v>
+        <v>-21.55</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.78</v>
+        <v>21.55</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.78</v>
+        <v>21.55</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.7332356754072666E-2</v>
+        <v>6.1246638871899295E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED6BEDD-FBF0-425F-9F22-E7CBF37046E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103D7598-3DA4-4C10-9BB7-1BB80EF5C678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.55</v>
+        <v>21.62</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21706.938607700002</v>
+        <v>21777.448385080002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.1246638871899295E-2</v>
+        <v>6.0049290381475551E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.0220175120805774E-2</v>
+        <v>5.0057575108851261E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5939675174013928E-2</v>
+        <v>4.5790934320074007E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5939675174013928E-2</v>
+        <v>4.5790934320074007E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5939675174013928E-2</v>
+        <v>4.5790934320074007E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.4292343387471E-2</v>
+        <v>5.411655874190565E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.9234338747099766E-2</v>
+        <v>2.9139685476410729E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0220175120805774E-2</v>
+        <v>5.0057575108851261E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.5179713622772963E-2</v>
+        <v>5.5001055900590068E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.5731624844180767E-2</v>
+        <v>5.555118017539757E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.2122951675721478E-2</v>
+        <v>4.1986568390924968E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.4669389337842674E-2</v>
+        <v>4.452476134276178E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.4999257644304838E-2</v>
+        <v>3.4885939048786736E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.3196934857842352E-2</v>
+        <v>4.3057074291697625E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.5376274880493865E-2</v>
+        <v>3.5261735600122239E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.4343471618589055E-2</v>
+        <v>3.4232276289574197E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.5155524267678283E-2</v>
+        <v>3.5041699721020676E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.2617747108237699E-2</v>
+        <v>3.2512139231384019E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8208197426411701E-2</v>
+        <v>5.8019734252505652E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8050719162812271E-2</v>
+        <v>5.7862765863025183E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1451419437092985E-2</v>
+        <v>5.1284832972680564E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7201735699226907E-2</v>
+        <v>4.7048908617869561E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8058376675324933E-2</v>
+        <v>3.7935153439095849E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4828181605250546E-2</v>
+        <v>4.4683039481644274E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5724740462707141E-2</v>
+        <v>3.5609072940394948E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9281049229785718E-2</v>
+        <v>2.9186244722566246E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1644944937391305E-2</v>
+        <v>3.1542486743791981E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8942963047637642E-2</v>
+        <v>2.884925317653058E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.55</v>
+        <v>-21.62</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.55</v>
+        <v>21.62</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.55</v>
+        <v>21.62</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.1246638871899295E-2</v>
+        <v>6.0049290381475551E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103D7598-3DA4-4C10-9BB7-1BB80EF5C678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52338E11-39B8-4BC9-8D42-E287794C483C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>21.62</v>
+        <v>22.34</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21777.448385080002</v>
+        <v>22502.691809560001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.0049290381475551E-2</v>
+        <v>4.803456216405988E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.0057575108851261E-2</v>
+        <v>4.8444260244107626E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5790934320074007E-2</v>
+        <v>4.4315129811996423E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5790934320074007E-2</v>
+        <v>4.4315129811996423E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5790934320074007E-2</v>
+        <v>4.4315129811996423E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.411655874190565E-2</v>
+        <v>5.2372426141450323E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.9139685476410729E-2</v>
+        <v>2.820053715308863E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0057575108851261E-2</v>
+        <v>4.8444260244107626E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.5001055900590068E-2</v>
+        <v>5.3228416677294423E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.555118017539757E-2</v>
+        <v>5.3760810894901319E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.1986568390924968E-2</v>
+        <v>4.0633375497394715E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.452476134276178E-2</v>
+        <v>4.3089764558214401E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.4885939048786736E-2</v>
+        <v>3.3761593654197369E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.3057074291697625E-2</v>
+        <v>4.1669379865107548E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.5261735600122239E-2</v>
+        <v>3.4125278588838084E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.4232276289574197E-2</v>
+        <v>3.3128997913186853E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.5041699721020676E-2</v>
+        <v>3.3912334286860656E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.2512139231384019E-2</v>
+        <v>3.1464299471017122E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8019734252505652E-2</v>
+        <v>5.6149805485191231E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7862765863025183E-2</v>
+        <v>5.5997896059024374E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1284832972680564E-2</v>
+        <v>4.9631964586810823E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7048908617869561E-2</v>
+        <v>4.5532560623023272E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7935153439095849E-2</v>
+        <v>3.6712534348847463E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4683039481644274E-2</v>
+        <v>4.3242941521627089E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5609072940394948E-2</v>
+        <v>3.4461421529603353E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9186244722566246E-2</v>
+        <v>2.8245595832671541E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1542486743791981E-2</v>
+        <v>3.0525898093141567E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.884925317653058E-2</v>
+        <v>2.7919465249623597E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-21.62</v>
+        <v>-22.34</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>21.62</v>
+        <v>22.34</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>21.62</v>
+        <v>22.34</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.0049290381475551E-2</v>
+        <v>4.803456216405988E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52338E11-39B8-4BC9-8D42-E287794C483C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A2D984-6A96-41FC-861E-88FC971CB579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.34</v>
+        <v>20.76</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22502.691809560001</v>
+        <v>20911.185405839999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>4.803456216405988E-2</v>
+        <v>7.5140533646880892E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.8444260244107626E-2</v>
+        <v>5.2131251149005992E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4315129811996423E-2</v>
+        <v>4.7687861271676305E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4315129811996423E-2</v>
+        <v>4.7687861271676305E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4315129811996423E-2</v>
+        <v>4.7687861271676305E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.2372426141450323E-2</v>
+        <v>5.6358381502890173E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.820053715308863E-2</v>
+        <v>3.0346820809248554E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8444260244107626E-2</v>
+        <v>5.2131251149005992E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.3228416677294423E-2</v>
+        <v>5.7279519680672318E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.3760810894901319E-2</v>
+        <v>5.7852433304050842E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.0633375497394715E-2</v>
+        <v>4.3725896368583712E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.3089764558214401E-2</v>
+        <v>4.6369236041932063E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.3761593654197369E-2</v>
+        <v>3.6331117641366532E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.1669379865107548E-2</v>
+        <v>4.4840748852914385E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.4125278588838084E-2</v>
+        <v>3.6722481872574313E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.3128997913186853E-2</v>
+        <v>3.5650376367080641E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.3912334286860656E-2</v>
+        <v>3.6493330826997447E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.1464299471017122E-2</v>
+        <v>3.3858981222664855E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6149805485191231E-2</v>
+        <v>6.0423249255258778E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5997896059024374E-2</v>
+        <v>6.0259778321705419E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9631964586810823E-2</v>
+        <v>5.3409349174824372E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5532560623023272E-2</v>
+        <v>4.8997948184891137E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6712534348847463E-2</v>
+        <v>3.9506648234742404E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3242941521627089E-2</v>
+        <v>4.6534070982328958E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4461421529603353E-2</v>
+        <v>3.7084207946596288E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8245595832671541E-2</v>
+        <v>3.0395308810302613E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0525898093141567E-2</v>
+        <v>3.28491600867429E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7919465249623597E-2</v>
+        <v>3.0044357113515954E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.34</v>
+        <v>-20.76</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.34</v>
+        <v>20.76</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.34</v>
+        <v>20.76</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>4.803456216405988E-2</v>
+        <v>7.5140533646880892E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A2D984-6A96-41FC-861E-88FC971CB579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C69A38-EF0C-4083-BE05-2D2DA49B0247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C69A38-EF0C-4083-BE05-2D2DA49B0247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DE0669-08B5-4D76-A85D-E24BA8491515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>20.76</v>
+        <v>20.66</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>20911.185405839999</v>
+        <v>20810.457152439998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.5140533646880892E-2</v>
+        <v>7.6950997735104387E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>11.165268338950117</v>
+        <v>10.865098595499758</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>15.642626483276317</v>
+        <v>13.504418281934191</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4544,7 +4544,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.2131251149005992E-2</v>
+        <v>5.2383580535012804E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.7687861271676305E-2</v>
+        <v>4.7918683446272994E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.7085179507794772</v>
+        <v>1.6789208962048472</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>9.4567503881706401</v>
+        <v>9.1861776992949107</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>11.165268338950117</v>
+        <v>10.865098595499758</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.50599309724395147</v>
+        <v>0.51927409692630511</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.1286241097705441</v>
+        <v>1.9324800000000002</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>13.514002373505772</v>
+        <v>11.571938281934191</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>15.642626483276317</v>
+        <v>13.504418281934191</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.30789254450648473</v>
+        <v>0.40249749074926611</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.7687861271676305E-2</v>
+        <v>4.7918683446272994E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.7687861271676305E-2</v>
+        <v>4.7918683446272994E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.6358381502890173E-2</v>
+        <v>5.6631171345595359E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.0346820809248554E-2</v>
+        <v>3.0493707647628269E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.2131251149005992E-2</v>
+        <v>5.2383580535012804E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7279519680672318E-2</v>
+        <v>5.755676808183724E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.7852433304050842E-2</v>
+        <v>5.8132454762444122E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.3725896368583712E-2</v>
+        <v>4.3937541559138329E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.6369236041932063E-2</v>
+        <v>4.65936757129966E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.6331117641366532E-2</v>
+        <v>3.6506970098488342E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.4840748852914385E-2</v>
+        <v>4.5057790231679704E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.6722481872574313E-2</v>
+        <v>3.6900228638656482E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.5650376367080641E-2</v>
+        <v>3.5822933851916469E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.6493330826997447E-2</v>
+        <v>3.6669968439906435E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.3858981222664855E-2</v>
+        <v>3.4022867869434772E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0423249255258778E-2</v>
+        <v>6.0715714159688884E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0259778321705419E-2</v>
+        <v>6.0551451982507484E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3409349174824372E-2</v>
+        <v>5.3667864901711229E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8997948184891137E-2</v>
+        <v>4.9235111535253631E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9506648234742404E-2</v>
+        <v>3.9697871120680177E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6534070982328958E-2</v>
+        <v>4.6759308499184381E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7084207946596288E-2</v>
+        <v>3.7263705564924442E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0395308810302613E-2</v>
+        <v>3.0542430343750353E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.28491600867429E-2</v>
+        <v>3.3008158925497709E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0044357113515954E-2</v>
+        <v>3.0189779945623971E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-20.76</v>
+        <v>-20.66</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>20.76</v>
+        <v>20.66</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.7085179507794772</v>
+        <v>1.6789208962048472</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>9.4567503881706401</v>
+        <v>9.1861776992949107</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19535,7 +19535,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>11.165268338950117</v>
+        <v>10.865098595499758</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.50599309724395147</v>
+        <v>0.51927409692630511</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>20.76</v>
+        <v>20.66</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>7.5140533646880892E-2</v>
+        <v>7.6950997735104387E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.1286241097705441</v>
+        <v>1.9324800000000002</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19614,7 +19614,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>13.514002373505772</v>
+        <v>11.571938281934191</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19624,7 +19624,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>15.642626483276317</v>
+        <v>13.504418281934191</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19635,7 +19635,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.30789254450648473</v>
+        <v>0.40249749074926611</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DE0669-08B5-4D76-A85D-E24BA8491515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DA1709-4F61-4BD0-BCE2-FE8B60100210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>20.66</v>
+        <v>20.64</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>20810.457152439998</v>
+        <v>20790.311501760003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.6950997735104387E-2</v>
+        <v>7.7314534751272479E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.2383580535012804E-2</v>
+        <v>5.2434339818476956E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.7918683446272994E-2</v>
+        <v>4.7965116279069769E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.7918683446272994E-2</v>
+        <v>4.7965116279069769E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.7918683446272994E-2</v>
+        <v>4.7965116279069769E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.6631171345595359E-2</v>
+        <v>5.6686046511627911E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.0493707647628269E-2</v>
+        <v>3.0523255813953487E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.2383580535012804E-2</v>
+        <v>5.2434339818476956E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.755676808183724E-2</v>
+        <v>5.7612540143932044E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.8132454762444122E-2</v>
+        <v>5.8188784660469742E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.3937541559138329E-2</v>
+        <v>4.3980116696308039E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.65936757129966E-2</v>
+        <v>4.6638824623571204E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.6506970098488342E-2</v>
+        <v>3.654234506951401E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.5057790231679704E-2</v>
+        <v>4.5101450881129004E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.6900228638656482E-2</v>
+        <v>3.6935984674159053E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.5822933851916469E-2</v>
+        <v>3.5857645997121809E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.6669968439906435E-2</v>
+        <v>3.6705501355061385E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.4022867869434772E-2</v>
+        <v>3.4055835764657094E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0715714159688884E-2</v>
+        <v>6.0774547216045159E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0551451982507484E-2</v>
+        <v>6.061012587008742E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3667864901711229E-2</v>
+        <v>5.3719868646771016E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9235111535253631E-2</v>
+        <v>4.9282819976663748E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9697871120680177E-2</v>
+        <v>3.9736338050060674E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6759308499184381E-2</v>
+        <v>4.6804617906644821E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7263705564924442E-2</v>
+        <v>3.729981380675091E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0542430343750353E-2</v>
+        <v>3.0572025721990418E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3008158925497709E-2</v>
+        <v>3.304014357561931E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0189779945623971E-2</v>
+        <v>3.0219033608361975E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-20.66</v>
+        <v>-20.64</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>20.66</v>
+        <v>20.64</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>20.66</v>
+        <v>20.64</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>7.6950997735104387E-2</v>
+        <v>7.7314534751272479E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DA1709-4F61-4BD0-BCE2-FE8B60100210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA22944-E568-45BF-9F30-78AA82A56990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>20.64</v>
+        <v>20.66</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>20790.311501760003</v>
+        <v>20810.457152439998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.7314534751272479E-2</v>
+        <v>7.6950997735104387E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.2434339818476956E-2</v>
+        <v>5.2383580535012804E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.7965116279069769E-2</v>
+        <v>4.7918683446272994E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.7965116279069769E-2</v>
+        <v>4.7918683446272994E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.7965116279069769E-2</v>
+        <v>4.7918683446272994E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.6686046511627911E-2</v>
+        <v>5.6631171345595359E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.0523255813953487E-2</v>
+        <v>3.0493707647628269E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.2434339818476956E-2</v>
+        <v>5.2383580535012804E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.7612540143932044E-2</v>
+        <v>5.755676808183724E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.8188784660469742E-2</v>
+        <v>5.8132454762444122E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.3980116696308039E-2</v>
+        <v>4.3937541559138329E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.6638824623571204E-2</v>
+        <v>4.65936757129966E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.654234506951401E-2</v>
+        <v>3.6506970098488342E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.5101450881129004E-2</v>
+        <v>4.5057790231679704E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.6935984674159053E-2</v>
+        <v>3.6900228638656482E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.5857645997121809E-2</v>
+        <v>3.5822933851916469E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.6705501355061385E-2</v>
+        <v>3.6669968439906435E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.4055835764657094E-2</v>
+        <v>3.4022867869434772E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0774547216045159E-2</v>
+        <v>6.0715714159688884E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.061012587008742E-2</v>
+        <v>6.0551451982507484E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3719868646771016E-2</v>
+        <v>5.3667864901711229E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9282819976663748E-2</v>
+        <v>4.9235111535253631E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9736338050060674E-2</v>
+        <v>3.9697871120680177E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6804617906644821E-2</v>
+        <v>4.6759308499184381E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.729981380675091E-2</v>
+        <v>3.7263705564924442E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0572025721990418E-2</v>
+        <v>3.0542430343750353E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.304014357561931E-2</v>
+        <v>3.3008158925497709E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0219033608361975E-2</v>
+        <v>3.0189779945623971E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-20.64</v>
+        <v>-20.66</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>20.64</v>
+        <v>20.66</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>20.64</v>
+        <v>20.66</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>7.7314534751272479E-2</v>
+        <v>7.6950997735104387E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA22944-E568-45BF-9F30-78AA82A56990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97635BD-0BB4-4771-B98E-28E0B7DA7C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>CN</t>
@@ -4240,13 +4244,13 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4277,7 +4281,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4324,10 +4328,10 @@
         <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4421,7 +4425,7 @@
         <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4429,7 +4433,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4442,7 +4446,7 @@
         <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4450,7 +4454,7 @@
         <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -6610,7 +6614,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12779,7 +12783,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19802,4 +19806,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97635BD-0BB4-4771-B98E-28E0B7DA7C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB7A9C8-0D1C-401B-B8D2-143AFC53E169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2504,7 +2517,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2944,6 +2957,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3147,11 +3166,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3936,9 +3956,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{BFFF83CC-F5EE-4EDB-87AA-0F1E3F47EB08}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4023,6 +4049,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>1007282534</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>20.66</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19809,22 +19918,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB122F96-AC4F-4B30-97DB-935D54F978AF}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB7A9C8-0D1C-401B-B8D2-143AFC53E169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85203036-64C3-472E-8105-CC554E6F6716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3920,47 +3920,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4449,7 +4449,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>20.66</v>
+        <v>21.11</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>20810.457152439998</v>
+        <v>21263.734292739999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4507,13 +4507,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4589,14 +4589,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>22.601441956902718</v>
+        <v>18.758424601634019</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.6950997735104387E-2</v>
+        <v>1.013906570406431E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>10.865098595499758</v>
+        <v>7.6314402727898702</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4638,7 +4638,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>13.504418281934191</v>
+        <v>10.336151389000461</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4657,7 +4657,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>21.622888321317863</v>
+        <v>17.674312632907508</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4676,7 +4676,7 @@
         <v>433</v>
       </c>
       <c r="F31" s="312">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>20.116801024749044</v>
+        <v>17.124648599063175</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4713,13 +4713,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4740,13 +4740,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4766,13 +4766,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4801,13 +4801,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4823,13 +4823,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4893,13 +4893,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4915,13 +4915,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4937,22 +4937,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.2383580535012804E-2</v>
+        <v>5.1266924389074583E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.7918683446272994E-2</v>
+        <v>4.6897205116058743E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -5087,13 +5087,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5146,22 +5146,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>18.037412897556077</v>
+        <v>14.429930318044859</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5198,13 +5198,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5217,13 +5217,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5345,13 +5345,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>20.824583863949179</v>
+        <v>17.217101284437963</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5390,13 +5390,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>27 CNY</v>
+        <v>22.49 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>23.64 CNY</v>
+        <v>19.67 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>22.43 CNY</v>
+        <v>18.62 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>21.34 CNY</v>
+        <v>17.66 CNY</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>20.82 CNY</v>
+        <v>17.22 CNY</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>22.601441956902718</v>
+        <v>18.758424601634019</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5539,13 +5539,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5558,22 +5558,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.6789208962048472</v>
+        <v>1.4783631965230226</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>9.1861776992949107</v>
+        <v>6.1530770762668476</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>10.865098595499758</v>
+        <v>7.6314402727898702</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51927409692630511</v>
+        <v>0.59317264456605234</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>1.9324800000000002</v>
+        <v>1.7979517523896227</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>11.571938281934191</v>
+        <v>8.5381996366108392</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>13.504418281934191</v>
+        <v>10.336151389000461</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.40249749074926611</v>
+        <v>0.44898616976075412</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>2.6462818299670237</v>
+        <v>2.5745204824732406</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>18.976606491350839</v>
+        <v>15.099792150434268</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>21.622888321317863</v>
+        <v>17.674312632907508</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>4.3296070996301839E-2</v>
+        <v>5.779333775353801E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>17.597359866884187</v>
+        <v>14.605207441198319</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>20.116801024749044</v>
+        <v>17.124648599063175</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.13177365640345884</v>
+        <v>0.11082961697715177</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5906,13 +5906,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5920,13 +5920,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5949,13 +5949,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5963,22 +5963,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6002,6 +6002,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6018,17 +6029,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13596,20 +13596,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.7918683446272994E-2</v>
+        <v>4.6897205116058743E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.7918683446272994E-2</v>
+        <v>4.6897205116058743E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.6631171345595359E-2</v>
+        <v>5.5423969682614885E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.0493707647628269E-2</v>
+        <v>2.9843675982946471E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14795,50 +14795,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.2383580535012804E-2</v>
+        <v>5.1266924389074583E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>5.755676808183724E-2</v>
+        <v>5.6329835555222994E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.8132454762444122E-2</v>
+        <v>5.6893250373855779E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.3937541559138329E-2</v>
+        <v>4.3000928877868209E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.65936757129966E-2</v>
+        <v>4.5600442455258634E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.6506970098488342E-2</v>
+        <v>3.5728754250818062E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.5057790231679704E-2</v>
+        <v>4.409729730869269E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>3.6900228638656482E-2</v>
+        <v>3.6113629733521689E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>3.5822933851916469E-2</v>
+        <v>3.5059299544319952E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>3.6669968439906435E-2</v>
+        <v>3.5888277971031127E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.4022867869434772E-2</v>
+        <v>3.3297605408930481E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14852,43 +14852,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0715714159688884E-2</v>
+        <v>5.9421442659363923E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0551451982507484E-2</v>
+        <v>5.9260682044462561E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3667864901711229E-2</v>
+        <v>5.2523831779694649E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9235111535253631E-2</v>
+        <v>4.8185571024080533E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9697871120680177E-2</v>
+        <v>3.8851635118581355E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6759308499184381E-2</v>
+        <v>4.5762544462015602E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7263705564924442E-2</v>
+        <v>3.6469358454350495E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0542430343750353E-2</v>
+        <v>2.9891360061671358E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3008158925497709E-2</v>
+        <v>3.2304526925664739E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0189779945623971E-2</v>
+        <v>2.9546227080842789E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15659,7 +15659,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15670,16 +15670,16 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>18168770970.254566</v>
+        <v>14535016776.203651</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15694,8 +15694,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15710,8 +15710,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15726,8 +15726,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>20976239603.974239</v>
+        <v>17342485409.923325</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15764,7 +15764,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>20.824583863949179</v>
+        <v>17.217101284437963</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>23.169996134207583</v>
+        <v>19.259130675097101</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15860,11 +15860,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>1072059985.528577</v>
+        <v>1057101008.9863179</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15882,11 +15882,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>1054293118.7192547</v>
+        <v>1025076255.8727571</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15904,11 +15904,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1036820695.8407583</v>
+        <v>994021688.96019888</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15936,11 +15936,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1019637837.1791052</v>
+        <v>963907916.5696106</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15968,11 +15968,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1002739743.8900673</v>
+        <v>934706437.43948519</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16000,11 +16000,11 @@
       </c>
       <c r="E26" s="124">
         <f t="shared" si="0"/>
-        <v>0.70496054043967626</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>986121696.65894628</v>
+        <v>906389613.75074446</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16022,11 +16022,11 @@
       </c>
       <c r="E27" s="124">
         <f t="shared" si="0"/>
-        <v>0.66505711362233599</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>969779054.38255894</v>
+        <v>878930644.96885097</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16044,11 +16044,11 @@
       </c>
       <c r="E28" s="124">
         <f t="shared" si="0"/>
-        <v>0.62741237134182648</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>953707252.87306607</v>
+        <v>852303542.47836936</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16066,11 +16066,11 @@
       </c>
       <c r="E29" s="124">
         <f t="shared" si="0"/>
-        <v>0.59189846353002495</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>937901803.58328032</v>
+        <v>826483104.98597038</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16088,11 +16088,11 @@
       </c>
       <c r="E30" s="124">
         <f t="shared" si="0"/>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>922358292.35310292</v>
+        <v>801444894.66859913</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16612,7 +16612,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>18939726411.004864</v>
+        <v>15151781128.80389</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16620,11 +16620,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>10575844304.106426</v>
+        <v>7351552206.6483564</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>20531263785.115143</v>
+        <v>16591917315.329262</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16656,7 +16656,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>20531263785.115143</v>
+        <v>16591917315.329262</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16686,19 +16686,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>18168770970.254559</v>
+        <v>14535016776.203655</v>
       </c>
       <c r="C56" s="123">
-        <v>18438672146.565094</v>
+        <v>14763830899.01115</v>
       </c>
       <c r="D56" s="123">
-        <v>18989004554.905563</v>
+        <v>15231384589.006489</v>
       </c>
       <c r="E56" s="123">
-        <v>19553895609.045933</v>
+        <v>15712658428.732964</v>
       </c>
       <c r="F56" s="123">
-        <v>19841999645.437908</v>
+        <v>15958626992.889118</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16707,19 +16707,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>18168770970.254555</v>
+        <v>14535016776.203655</v>
       </c>
       <c r="C57" s="123">
-        <v>18684739930.911228</v>
+        <v>14983213702.839741</v>
       </c>
       <c r="D57" s="123">
-        <v>19790310038.934723</v>
+        <v>15945591177.761124</v>
       </c>
       <c r="E57" s="123">
-        <v>21003955532.407841</v>
+        <v>17004731376.087135</v>
       </c>
       <c r="F57" s="123">
-        <v>21655330203.675339</v>
+        <v>17574156384.06876</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16728,19 +16728,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>18168770970.254551</v>
+        <v>14535016776.203655</v>
       </c>
       <c r="C58" s="341">
-        <v>19010101200.11388</v>
+        <v>15254072754.866863</v>
       </c>
       <c r="D58" s="123">
-        <v>20905117839.794746</v>
+        <v>16873380060.141762</v>
       </c>
       <c r="E58" s="123">
-        <v>23130744582.736561</v>
+        <v>18774183713.476677</v>
       </c>
       <c r="F58" s="123">
-        <v>24387958794.966114</v>
+        <v>19847292877.083092</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16759,19 +16759,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>18168770970.254551</v>
+        <v>14535016776.203655</v>
       </c>
       <c r="C59" s="341">
-        <v>19364349053.217316</v>
+        <v>15529162324.863256</v>
       </c>
       <c r="D59" s="123">
-        <v>22185188314.298473</v>
+        <v>17867109392.317905</v>
       </c>
       <c r="E59" s="123">
-        <v>25714936261.325912</v>
+        <v>20779654377.961792</v>
       </c>
       <c r="F59" s="123">
-        <v>27807540354.755692</v>
+        <v>22500614269.24242</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16790,19 +16790,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>18168770970.254551</v>
+        <v>14535016776.203653</v>
       </c>
       <c r="C60" s="341">
-        <v>19716333824.36945</v>
+        <v>15784045830.885729</v>
       </c>
       <c r="D60" s="123">
-        <v>23528975663.756058</v>
+        <v>18839882964.73716</v>
       </c>
       <c r="E60" s="123">
-        <v>28594872247.096466</v>
+        <v>22863732750.220058</v>
       </c>
       <c r="F60" s="123">
-        <v>31740453134.6306</v>
+        <v>25346163484.426208</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16821,19 +16821,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>18168770970.254547</v>
+        <v>14535016776.203653</v>
       </c>
       <c r="C61" s="341">
-        <v>20047897203.448524</v>
+        <v>16007904642.795082</v>
       </c>
       <c r="D61" s="123">
-        <v>24868592519.505997</v>
+        <v>19744048090.652229</v>
       </c>
       <c r="E61" s="123">
-        <v>31651883772.804543</v>
+        <v>24926295692.135139</v>
       </c>
       <c r="F61" s="123">
-        <v>36056956864.10157</v>
+        <v>28257942663.635319</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16913,23 +16913,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>20.824583863949179</v>
+        <v>17.217101284437963</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>20.824583863949179</v>
+        <v>17.217101284437963</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>20.824583863949179</v>
+        <v>17.217101284437963</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>20.824583863949179</v>
+        <v>17.217101284437963</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>20.824583863949179</v>
+        <v>17.217101284437963</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16940,23 +16940,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20.824583863949172</v>
+        <v>17.217101284437966</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>21.092533686566206</v>
+        <v>17.444261108106161</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>21.63888725645792</v>
+        <v>17.908434440029872</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>22.199694214856311</v>
+        <v>18.386228726619258</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>22.48571529302183</v>
+        <v>18.630418967047028</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16967,23 +16967,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>20.824583863949172</v>
+        <v>17.217101284437966</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>21.336822429833674</v>
+        <v>17.662057800120074</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>22.4343993962814</v>
+        <v>18.617477399325978</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>23.639270375879974</v>
+        <v>19.668960138850984</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>24.285935685046848</v>
+        <v>20.234268271138745</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16994,23 +16994,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>20.824583863949162</v>
+        <v>17.217101284437966</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>21.65983137540788</v>
+        <v>17.93095857312516</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>23.541147268135223</v>
+        <v>19.538558477438503</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>25.750682992043455</v>
+        <v>21.425619544393246</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>26.998807693696978</v>
+        <v>22.490970255226095</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17021,23 +17021,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>20.824583863949162</v>
+        <v>17.217101284437966</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>22.011518058285912</v>
+        <v>18.20405927795322</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>24.811962983980568</v>
+        <v>20.525103263666416</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>28.316191269375857</v>
+        <v>23.416590892343883</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>30.393666081849652</v>
+        <v>25.125108446447154</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17048,23 +17048,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>20.824583863949162</v>
+        <v>17.217101284437966</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>22.360958021028409</v>
+        <v>18.457100006268355</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>26.146034909283689</v>
+        <v>21.490843797810591</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>31.175305657405694</v>
+        <v>25.485601623605369</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>34.298144365868922</v>
+        <v>27.950084676188663</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17074,23 +17074,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>20.824583863949162</v>
+        <v>17.217101284437966</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>22.690124235955629</v>
+        <v>18.679340345352159</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>27.475966493057125</v>
+        <v>22.38847191643244</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>34.210215350089861</v>
+        <v>27.533252478549198</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>38.583440282129665</v>
+        <v>30.840812035121608</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>26.998807693696978</v>
+        <v>22.490970255226095</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>23.639270375879974</v>
+        <v>19.668960138850984</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>22.4343993962814</v>
+        <v>18.617477399325978</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>21.336822429833674</v>
+        <v>17.662057800120074</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>20.824583863949162</v>
+        <v>17.217101284437966</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17419,7 +17419,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17430,14 +17430,14 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>16620161811.000002</v>
+        <v>13296129448.800001</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>16.500000000000004</v>
+        <v>13.200000000000001</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17499,7 +17499,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>18.645501834384856</v>
+        <v>15.067977693765656</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17542,11 +17542,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>980683308.7254014</v>
+        <v>966999355.58039582</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17564,11 +17564,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>964430794.90766108</v>
+        <v>937704221.66208613</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17586,11 +17586,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>948447628.19009626</v>
+        <v>909296580.44616449</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17608,11 +17608,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>932729344.77952528</v>
+        <v>881749545.44359887</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17630,11 +17630,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>917271554.85961366</v>
+        <v>855037044.68844044</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17652,11 +17652,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" si="0"/>
-        <v>0.70496054043967626</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>902069941.36488426</v>
+        <v>829133796.06194115</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -17674,11 +17674,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.66505711362233599</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>887120258.77504206</v>
+        <v>804015283.36422336</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -17696,11 +17696,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.62741237134182648</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>872418331.92928219</v>
+        <v>779657733.11085653</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -17718,11 +17718,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.59189846353002495</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>857960054.86024642</v>
+        <v>756038092.03237855</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -17740,11 +17740,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>843741389.64730573</v>
+        <v>733134005.2554661</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>17325405120.815426</v>
+        <v>13860324096.652342</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18202,11 +18202,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9674415727.4017696</v>
+        <v>6724945095.9861956</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18217,7 +18217,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>18781288335.440826</v>
+        <v>15177710753.631746</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18238,7 +18238,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>18781288335.440826</v>
+        <v>15177710753.631746</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18268,19 +18268,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>16620161810.999996</v>
+        <v>13296129448.800003</v>
       </c>
       <c r="C51" s="123">
-        <v>16867058050.189999</v>
+        <v>13505440675.84605</v>
       </c>
       <c r="D51" s="123">
-        <v>17370483058.487511</v>
+        <v>13933142582.363274</v>
       </c>
       <c r="E51" s="123">
-        <v>17887225811.245522</v>
+        <v>14373395206.206177</v>
       </c>
       <c r="F51" s="123">
-        <v>18150773395.783642</v>
+        <v>14598398721.490036</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18289,19 +18289,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>16620161810.999994</v>
+        <v>13296129448.800003</v>
       </c>
       <c r="C52" s="123">
-        <v>17092152328.663898</v>
+        <v>13706124459.253935</v>
       </c>
       <c r="D52" s="123">
-        <v>18103489535.723083</v>
+        <v>14586474009.73489</v>
       </c>
       <c r="E52" s="123">
-        <v>19213690358.648178</v>
+        <v>15555338745.028885</v>
       </c>
       <c r="F52" s="123">
-        <v>19809545326.151299</v>
+        <v>16076229001.578363</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18310,19 +18310,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>16620161810.999989</v>
+        <v>13296129448.800003</v>
       </c>
       <c r="C53" s="123">
-        <v>17389781538.148323</v>
+        <v>13953896929.941961</v>
       </c>
       <c r="D53" s="123">
-        <v>19123277063.937992</v>
+        <v>15435183114.872395</v>
       </c>
       <c r="E53" s="123">
-        <v>21159203250.642715</v>
+        <v>17173972400.129349</v>
       </c>
       <c r="F53" s="123">
-        <v>22309259227.05151</v>
+        <v>18155615460.587593</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18331,19 +18331,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>16620161810.999989</v>
+        <v>13296129448.800005</v>
       </c>
       <c r="C54" s="123">
-        <v>17713835193.148849</v>
+        <v>14205539331.805229</v>
       </c>
       <c r="D54" s="123">
-        <v>20294241156.697281</v>
+        <v>16344212257.467888</v>
       </c>
       <c r="E54" s="123">
-        <v>23523132209.79525</v>
+        <v>19008507438.604179</v>
       </c>
       <c r="F54" s="123">
-        <v>25437373888.338268</v>
+        <v>20582781885.134026</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18352,19 +18352,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>16620161810.999985</v>
+        <v>13296129448.800003</v>
       </c>
       <c r="C55" s="123">
-        <v>18035818659.236553</v>
+        <v>14438697926.846352</v>
       </c>
       <c r="D55" s="123">
-        <v>21523491237.736034</v>
+        <v>17234071797.529335</v>
       </c>
       <c r="E55" s="123">
-        <v>26157597808.331974</v>
+        <v>20914950082.988102</v>
       </c>
       <c r="F55" s="123">
-        <v>29035066153.659107</v>
+        <v>23185791658.05407</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18373,19 +18373,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>16620161810.999983</v>
+        <v>13296129448.800005</v>
       </c>
       <c r="C56" s="123">
-        <v>18339121343.821991</v>
+        <v>14643476207.272854</v>
       </c>
       <c r="D56" s="123">
-        <v>22748926295.713158</v>
+        <v>18061170709.237457</v>
       </c>
       <c r="E56" s="123">
-        <v>28954045971.971764</v>
+        <v>22801711157.588223</v>
       </c>
       <c r="F56" s="123">
-        <v>32983654121.389282</v>
+        <v>25849386306.012703</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18435,23 +18435,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>16.500000000000004</v>
+        <v>13.200000000000001</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>16.500000000000004</v>
+        <v>13.200000000000001</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>16.500000000000004</v>
+        <v>13.200000000000001</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>16.500000000000004</v>
+        <v>13.200000000000001</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>16.500000000000004</v>
+        <v>13.200000000000001</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18462,23 +18462,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>16.499999999999996</v>
+        <v>13.200000000000003</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>16.745111208480459</v>
+        <v>13.407797931544447</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>17.244896513302901</v>
+        <v>13.83240760368756</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>17.757903276863054</v>
+        <v>14.269477252949347</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>18.019545443427337</v>
+        <v>14.492854019337177</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18489,23 +18489,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>16.499999999999993</v>
+        <v>13.200000000000003</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>16.968578081851163</v>
+        <v>13.607030794851383</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>17.972603440102024</v>
+        <v>14.481015521842544</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>19.074777641928396</v>
+        <v>15.442875479293166</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>19.666324648245414</v>
+        <v>15.95999976068121</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18516,23 +18516,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>16.499999999999989</v>
+        <v>13.200000000000003</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>17.264055467230332</v>
+        <v>13.853011899779412</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>18.985018024682628</v>
+        <v>15.323588560180866</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>21.006224705016791</v>
+        <v>17.049806603843436</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>22.147965912264603</v>
+        <v>18.024352500673455</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18543,23 +18543,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>16.499999999999989</v>
+        <v>13.200000000000005</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>17.585766252498974</v>
+        <v>14.102834956736407</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>20.147516185064003</v>
+        <v>16.226045529215824</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>23.35306273641319</v>
+        <v>18.871078170212947</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>25.253464673237616</v>
+        <v>20.433970798042274</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18570,23 +18570,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>16.499999999999986</v>
+        <v>13.200000000000003</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>17.905421816076633</v>
+        <v>14.334307842616033</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>21.367878932899313</v>
+        <v>17.109471489683681</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>25.968481459177148</v>
+        <v>20.763737458976035</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>28.825146047513126</v>
+        <v>23.0181611171013</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18596,23 +18596,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>16.499999999999982</v>
+        <v>13.200000000000005</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>18.206531658000525</v>
+        <v>14.537605600210728</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>22.584454239840078</v>
+        <v>17.930590573744087</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>28.744711632190143</v>
+        <v>22.636857473385142</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>32.745186189626992</v>
+        <v>25.662498289693072</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>22.147965912264603</v>
+        <v>18.024352500673455</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>19.074777641928396</v>
+        <v>15.442875479293166</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>17.972603440102024</v>
+        <v>14.481015521842544</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>16.968578081851163</v>
+        <v>13.607030794851383</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>16.499999999999989</v>
+        <v>13.200000000000003</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18838,7 +18838,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-20.66</v>
+        <v>-21.11</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18887,7 +18887,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>23.591441956902717</v>
+        <v>19.748424601634017</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18902,11 +18902,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国国贸(600007.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18927,8 +18927,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18949,8 +18949,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18960,8 +18960,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18974,8 +18974,8 @@
       <c r="B11" s="159" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18993,8 +18993,8 @@
         <v>2.9436096404119594E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19011,8 +19011,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.4272741432500604E-2</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19029,8 +19029,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>7.2975508413014145E-2</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19056,21 +19056,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19078,14 +19078,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>20.66</v>
+        <v>21.11</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19093,14 +19093,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>20.824583863949179</v>
+        <v>17.217101284437963</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19120,8 +19120,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19131,8 +19131,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19140,14 +19140,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>22.4343993962814</v>
+        <v>18.617477399325978</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19157,8 +19157,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19178,8 +19178,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19189,8 +19189,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19198,14 +19198,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>21.336822429833674</v>
+        <v>17.662057800120074</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19215,8 +19215,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19236,8 +19236,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19247,8 +19247,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19256,14 +19256,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>23.639270375879974</v>
+        <v>19.668960138850984</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -19274,8 +19274,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>22.455858198911567</v>
+        <v>18.636690027389797</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19337,8 +19337,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="370"/>
+      <c r="F49" s="370"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19348,8 +19348,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19357,14 +19357,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>20.824583863949162</v>
+        <v>17.217101284437966</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="370"/>
+      <c r="F51" s="370"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19374,8 +19374,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="370"/>
+      <c r="F52" s="370"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19395,8 +19395,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="370"/>
+      <c r="F55" s="370"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19406,8 +19406,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="370"/>
+      <c r="F56" s="370"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19415,14 +19415,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>26.998807693696978</v>
+        <v>22.490970255226095</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="370"/>
+      <c r="F57" s="370"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19432,8 +19432,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19441,7 +19441,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>22.601441956902718</v>
+        <v>18.758424601634019</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>23.169996134207583</v>
+        <v>19.259130675097101</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.12331828082950577</v>
+        <v>0.148582358358085</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19617,7 +19617,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6789208962048472</v>
+        <v>1.4783631965230226</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>9.1861776992949107</v>
+        <v>6.1530770762668476</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>10.865098595499758</v>
+        <v>7.6314402727898702</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.51927409692630511</v>
+        <v>0.59317264456605234</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19676,7 +19676,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>20.66</v>
+        <v>21.11</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>7.6950997735104387E-2</v>
+        <v>1.013906570406431E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.9324800000000002</v>
+        <v>1.7979517523896227</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>11.571938281934191</v>
+        <v>8.5381996366108392</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>13.504418281934191</v>
+        <v>10.336151389000461</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.40249749074926611</v>
+        <v>0.44898616976075412</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.6462818299670237</v>
+        <v>2.5745204824732406</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>18.976606491350839</v>
+        <v>15.099792150434268</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>21.622888321317863</v>
+        <v>17.674312632907508</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>4.3296070996301839E-2</v>
+        <v>5.779333775353801E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>17.597359866884187</v>
+        <v>14.605207441198319</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>20.116801024749044</v>
+        <v>17.124648599063175</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.13177365640345884</v>
+        <v>0.11082961697715177</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19922,19 +19922,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="372"/>
+    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="360"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="370" t="s">
+      <c r="B2" s="358" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/600007.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600007.SS_Valuation.xlsx
@@ -8,45 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85203036-64C3-472E-8105-CC554E6F6716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEB794F-360E-47E4-B016-DA8F3655DC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="DDM" sheetId="10" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId3"/>
+    <sheet name="BS" sheetId="3" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId7"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
-    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,20 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="561">
   <si>
     <t>Sales</t>
   </si>
@@ -411,10 +406,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1348,10 +1339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1504,10 +1491,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1525,10 +1508,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1760,71 +1739,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1864,32 +1783,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1987,30 +1880,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2034,58 +1903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2103,23 +1920,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2162,10 +1962,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2284,10 +2080,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2334,133 +2126,1148 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
   <si>
     <t>CN</t>
@@ -3171,7 +3978,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3920,33 +4727,55 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3961,10 +4790,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{BFFF83CC-F5EE-4EDB-87AA-0F1E3F47EB08}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{62EA55F0-13E2-4EFB-9FB0-6C66107188BC}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4076,7 +4910,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>20.66</v>
+            <v>21.11</v>
           </cell>
         </row>
         <row r="13">
@@ -4101,7 +4935,7 @@
         </row>
         <row r="86">
           <cell r="C86">
-            <v>0.06</v>
+            <v>7.4999999999999997E-2</v>
           </cell>
         </row>
         <row r="92">
@@ -4331,6 +5165,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45797</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>CN</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>中国国贸</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>1007282534</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>600007.SS</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>21.11</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>21263.734292739999</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>RES_01</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (CNY) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>18.758424601634019</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>1.013906570406431E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>600007.SS (CNY)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>7.6314402727898702</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>10.336151389000461</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>17.674312632907508</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>17.124648599063175</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>1545350950.0180476</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>462652711</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>-490634169.24661446</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-53103191</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>-53103191</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-1078102.8016474061</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-373061939.75451189</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>1197782656</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>1090126258.2152739</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>5.1266924389074583E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>4.6897205116058743E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>1.0164059245889612</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>0.15161114820375229</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>0.16779050789746269</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>0.3932476207375345</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>0.41423799416800827</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.30212796693987309</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.31742662653511533</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.2760688428830085</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.2760688428830085</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>14.429930318044859</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>1232137409</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.2232292007557037</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>0.12757636177577109</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>0.79731882844192148</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>3986106600</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>3438409570.5196743</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>3.4135502745843049</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>601196472.20000005</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.59684989256450272</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>17.217101284437963</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>2.5713378719718771</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.06</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>15</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>22.49 CNY</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.05</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>10</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>19.67 CNY</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.03</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>10</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>18.62 CNY</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.01</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>10</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>17.66 CNY</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>15</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>17.22 CNY</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>18.758424601634019</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>600007.SS</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>1.4783631965230226</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>6.1530770762668476</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>7.6314402727898702</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.59317264456605234</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>1.7979517523896227</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>8.5381996366108392</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>10.336151389000461</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.44898616976075412</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>2.5745204824732406</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>15.099792150434268</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>17.674312632907508</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>5.779333775353801E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>2.5194411578648568</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>14.605207441198319</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>17.124648599063175</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.11082961697715177</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4347,24 +6924,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4378,7 +6955,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4387,15 +6964,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C6" s="51">
         <v>1007282534</v>
@@ -4404,7 +6981,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4414,7 +6991,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4427,26 +7004,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="C12" s="50">
         <v>21.11</v>
@@ -4456,17 +7033,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4480,7 +7057,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4494,7 +7071,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="C16" s="50">
         <v>1</v>
@@ -4507,71 +7084,71 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="361" t="s">
-        <v>356</v>
-      </c>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="361"/>
-      <c r="F18" s="361"/>
+      <c r="B18" s="371" t="s">
+        <v>468</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>464</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
         <v/>
       </c>
       <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4592,7 +7169,7 @@
         <v>18.758424601634019</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4605,7 +7182,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4616,7 +7193,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4624,7 +7201,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4635,7 +7212,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F29" s="302">
         <v>0.45</v>
@@ -4643,7 +7220,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4654,7 +7231,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F30" s="312">
         <v>0.3</v>
@@ -4662,7 +7239,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4673,7 +7250,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4681,7 +7258,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4692,7 +7269,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4704,7 +7281,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4712,27 +7289,27 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="361" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="361"/>
-      <c r="F36" s="361"/>
+    <row r="36" spans="1:6">
+      <c r="B36" s="371" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
-        <v>336</v>
-      </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4740,17 +7317,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="362" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
+      <c r="B40" s="367" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4766,17 +7343,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="362" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="362"/>
-      <c r="D43" s="362"/>
-      <c r="E43" s="362"/>
-      <c r="F43" s="362"/>
+      <c r="B43" s="367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4789,7 +7366,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4801,17 +7378,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="362" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="362"/>
-      <c r="D47" s="362"/>
-      <c r="E47" s="362"/>
-      <c r="F47" s="362"/>
+      <c r="B47" s="367" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4823,17 +7400,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="362" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="362"/>
-      <c r="D50" s="362"/>
-      <c r="E50" s="362"/>
-      <c r="F50" s="362"/>
+      <c r="B50" s="367" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4848,7 +7425,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4863,7 +7440,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4876,12 +7453,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4893,17 +7470,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="362" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="362"/>
-      <c r="D58" s="362"/>
-      <c r="E58" s="362"/>
-      <c r="F58" s="362"/>
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4915,17 +7492,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="362" t="s">
-        <v>335</v>
-      </c>
-      <c r="C61" s="365"/>
-      <c r="D61" s="365"/>
-      <c r="E61" s="365"/>
-      <c r="F61" s="365"/>
+      <c r="B61" s="367" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4937,26 +7514,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="361" t="s">
-        <v>340</v>
-      </c>
-      <c r="C64" s="361"/>
-      <c r="D64" s="361"/>
-      <c r="E64" s="361"/>
-      <c r="F64" s="361"/>
+      <c r="B64" s="371" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="361" t="s">
-        <v>358</v>
-      </c>
-      <c r="C65" s="361"/>
-      <c r="D65" s="361"/>
-      <c r="E65" s="361"/>
-      <c r="F65" s="361"/>
+      <c r="B65" s="371" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4969,7 +7546,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4982,7 +7559,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -4992,14 +7569,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>4.6897205116058743E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -5008,18 +7585,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -5074,7 +7651,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -5085,33 +7662,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="361" t="s">
-        <v>359</v>
-      </c>
-      <c r="C80" s="361"/>
-      <c r="D80" s="361"/>
-      <c r="E80" s="361"/>
-      <c r="F80" s="361"/>
+      <c r="B80" s="371" t="s">
+        <v>471</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5120,7 +7697,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5129,7 +7706,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5141,31 +7718,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="361" t="s">
-        <v>360</v>
-      </c>
-      <c r="C89" s="361"/>
-      <c r="D89" s="361"/>
-      <c r="E89" s="361"/>
-      <c r="F89" s="361"/>
+      <c r="B89" s="371" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="361" t="s">
-        <v>361</v>
-      </c>
-      <c r="C90" s="361"/>
-      <c r="D90" s="361"/>
-      <c r="E90" s="361"/>
-      <c r="F90" s="361"/>
+      <c r="B90" s="371" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5173,7 +7750,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5186,7 +7763,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5198,36 +7775,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="361" t="s">
-        <v>362</v>
-      </c>
-      <c r="C97" s="361"/>
-      <c r="D97" s="361"/>
-      <c r="E97" s="361"/>
-      <c r="F97" s="361"/>
+      <c r="B97" s="371" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="361" t="s">
-        <v>341</v>
-      </c>
-      <c r="C101" s="361"/>
-      <c r="D101" s="361"/>
-      <c r="E101" s="361"/>
-      <c r="F101" s="361"/>
+      <c r="B101" s="371" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5240,7 +7817,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5253,7 +7830,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5262,7 +7839,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5271,12 +7848,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5289,7 +7866,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5302,7 +7879,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5315,12 +7892,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5333,7 +7910,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5345,17 +7922,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="361" t="s">
-        <v>363</v>
-      </c>
-      <c r="C116" s="361"/>
-      <c r="D116" s="361"/>
-      <c r="E116" s="361"/>
-      <c r="F116" s="361"/>
+      <c r="B116" s="371" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5368,7 +7945,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5381,7 +7958,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5389,30 +7966,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="362" t="s">
-        <v>364</v>
-      </c>
-      <c r="C123" s="362"/>
-      <c r="D123" s="362"/>
-      <c r="E123" s="362"/>
-      <c r="F123" s="362"/>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>473</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5527,7 +8104,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5539,17 +8116,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="366" t="s">
-        <v>367</v>
-      </c>
-      <c r="C134" s="366"/>
-      <c r="D134" s="366"/>
-      <c r="E134" s="366"/>
-      <c r="F134" s="366"/>
+      <c r="B134" s="369" t="s">
+        <v>474</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5558,31 +8135,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="364" t="s">
-        <v>365</v>
-      </c>
-      <c r="C138" s="364"/>
-      <c r="D138" s="364"/>
-      <c r="E138" s="364"/>
-      <c r="F138" s="364"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="361" t="s">
-        <v>366</v>
-      </c>
-      <c r="C139" s="361"/>
-      <c r="D139" s="361"/>
-      <c r="E139" s="361"/>
-      <c r="F139" s="361"/>
+      <c r="B138" s="370" t="s">
+        <v>353</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="B139" s="371" t="s">
+        <v>476</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5591,7 +8168,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5600,7 +8177,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5613,7 +8190,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5626,7 +8203,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5655,7 +8232,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5668,7 +8245,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5681,7 +8258,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5690,12 +8267,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5724,7 +8301,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5737,7 +8314,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5750,7 +8327,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5759,12 +8336,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5793,7 +8370,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5806,7 +8383,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5819,7 +8396,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5828,12 +8405,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5862,7 +8439,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5875,7 +8452,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5888,7 +8465,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5897,7 +8474,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5906,113 +8483,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="368" t="s">
-        <v>373</v>
-      </c>
-      <c r="C179" s="361"/>
-      <c r="D179" s="361"/>
-      <c r="E179" s="361"/>
-      <c r="F179" s="361"/>
+      <c r="B179" s="372" t="s">
+        <v>477</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="365" t="s">
-        <v>377</v>
-      </c>
-      <c r="C182" s="365"/>
-      <c r="D182" s="365"/>
-      <c r="E182" s="365"/>
-      <c r="F182" s="365"/>
+      <c r="B182" s="373" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="362" t="s">
-        <v>378</v>
-      </c>
-      <c r="C188" s="362"/>
-      <c r="D188" s="362"/>
-      <c r="E188" s="362"/>
-      <c r="F188" s="362"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="34.35" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>478</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="367" t="s">
-        <v>379</v>
-      </c>
-      <c r="C191" s="367"/>
-      <c r="D191" s="367"/>
-      <c r="E191" s="367"/>
-      <c r="F191" s="367"/>
+      <c r="B191" s="368" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="367" t="s">
-        <v>380</v>
-      </c>
-      <c r="C192" s="367"/>
-      <c r="D192" s="367"/>
-      <c r="E192" s="367"/>
-      <c r="F192" s="367"/>
+      <c r="B192" s="368" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6029,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6053,7 +8630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6118,7 +8695,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6134,7 +8711,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="106">
         <v>1</v>
@@ -6142,7 +8719,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="351">
         <v>3912067946</v>
@@ -6178,7 +8755,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="351">
         <v>2022497629</v>
@@ -6214,7 +8791,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="351">
         <v>215939947</v>
@@ -6250,7 +8827,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="352">
         <v>89269733</v>
@@ -6286,7 +8863,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="351"/>
       <c r="D8" s="351"/>
@@ -6302,7 +8879,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6318,7 +8895,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6334,7 +8911,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6350,7 +8927,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="351">
         <v>53103191</v>
@@ -6380,7 +8957,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="351">
         <v>44666271</v>
@@ -6410,7 +8987,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="351">
         <v>421611829</v>
@@ -6446,7 +9023,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="353">
         <v>1263521768</v>
@@ -6482,7 +9059,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="351">
         <v>1132694</v>
@@ -6518,13 +9095,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="351">
         <v>462652711</v>
@@ -6554,7 +9131,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="351"/>
       <c r="D20" s="351"/>
@@ -6570,7 +9147,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="351"/>
       <c r="D21" s="351"/>
@@ -6586,7 +9163,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C22" s="351">
         <v>1796295378</v>
@@ -6622,7 +9199,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C23" s="351">
         <v>-63639368</v>
@@ -6658,7 +9235,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C24" s="351">
         <v>-1858931831</v>
@@ -6720,15 +9297,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>465</v>
+        <v>559</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
@@ -6765,7 +9342,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
@@ -6802,7 +9379,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
@@ -6839,7 +9416,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
@@ -6876,7 +9453,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6913,7 +9490,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6929,12 +9506,12 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="333">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -6983,7 +9560,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="333">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7032,7 +9609,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="329">
         <f>IF(C36="","",C36+C37)</f>
@@ -7081,7 +9658,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="333">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7130,7 +9707,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="346">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7179,7 +9756,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C41" s="346">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7228,7 +9805,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="333">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7277,7 +9854,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7326,7 +9903,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7375,7 +9952,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="349">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7424,7 +10001,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="333">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -7473,7 +10050,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="334">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -7522,7 +10099,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="333">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -7571,12 +10148,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="333">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -7625,7 +10202,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="333">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -7674,12 +10251,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7728,7 +10305,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7777,7 +10354,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7826,7 +10403,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7875,13 +10452,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" s="333">
         <f>IF(C$4="","",-C19)</f>
@@ -7930,7 +10507,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="333">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -7979,7 +10556,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="333">
         <f>IF(C$4="","",-C21)</f>
@@ -8028,7 +10605,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8077,7 +10654,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
@@ -8126,7 +10703,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8181,7 +10758,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8280,7 +10857,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8379,7 +10956,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -8395,13 +10972,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
@@ -8450,7 +11027,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -8484,7 +11061,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
@@ -8518,7 +11095,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -8567,7 +11144,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -8639,7 +11216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8659,7 +11236,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="99">
         <v>45657</v>
@@ -8675,7 +11252,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8686,27 +11263,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="19">
         <f>222388649+6185551</f>
@@ -8717,7 +11294,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="19">
         <v>3986106599</v>
@@ -8728,7 +11305,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -8738,7 +11315,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -8749,7 +11326,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="19">
         <v>30681363</v>
@@ -8759,7 +11336,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8770,7 +11347,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8780,7 +11357,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8791,7 +11368,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8801,7 +11378,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8812,7 +11389,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="19">
         <v>32164761</v>
@@ -8822,7 +11399,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8833,7 +11410,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="19">
         <v>0</v>
@@ -8845,7 +11422,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="19">
         <v>171668</v>
@@ -8857,7 +11434,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8868,7 +11445,7 @@
         <v>155710261</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8886,27 +11463,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>185</v>
-      </c>
       <c r="G14" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H14" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8915,7 +11492,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19">
         <v>1</v>
@@ -8926,7 +11503,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -8935,7 +11512,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8946,7 +11523,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8955,7 +11532,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8966,7 +11543,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="19">
         <v>1386748288</v>
@@ -8975,7 +11552,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8986,7 +11563,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="19">
         <f>35040471</f>
@@ -8996,7 +11573,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="19">
         <v>28358189</v>
@@ -9007,7 +11584,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -9016,7 +11593,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -9027,7 +11604,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="19">
         <v>432849427</v>
@@ -9036,7 +11613,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19">
         <v>5983606533</v>
@@ -9047,7 +11624,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="19">
         <v>66341579</v>
@@ -9059,7 +11636,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19">
         <f>79921743+33757144</f>
@@ -9072,7 +11649,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -9083,7 +11660,7 @@
         <v>916902912.35000002</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -9096,30 +11673,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H26" s="186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19">
         <v>111425305</v>
       </c>
       <c r="F27" s="187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
@@ -9132,13 +11709,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G28" s="12">
         <v>4958355</v>
@@ -9147,13 +11724,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="190" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9166,13 +11743,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
@@ -9182,14 +11759,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>111425305</v>
       </c>
       <c r="F31" s="190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
@@ -9199,14 +11776,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>1434146094</v>
       </c>
       <c r="F32" s="192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
@@ -9219,7 +11796,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="84">
         <v>1545571399</v>
@@ -